--- a/media/price_lists/ansal.xlsx
+++ b/media/price_lists/ansal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3409"/>
+  <dimension ref="A1:D3841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68598,6 +68598,8646 @@
         </is>
       </c>
     </row>
+    <row r="3410">
+      <c r="A3410" t="inlineStr">
+        <is>
+          <t>937181</t>
+        </is>
+      </c>
+      <c r="B3410" t="inlineStr">
+        <is>
+          <t>PCB Main S4UW18KL3AA/KLRPA EBR82278538</t>
+        </is>
+      </c>
+      <c r="C3410" t="n">
+        <v>230200.85</v>
+      </c>
+      <c r="D3410" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937181</t>
+        </is>
+      </c>
+    </row>
+    <row r="3411">
+      <c r="A3411" t="inlineStr">
+        <is>
+          <t>999589</t>
+        </is>
+      </c>
+      <c r="B3411" t="inlineStr">
+        <is>
+          <t>Calefact.GOODMAN GMP75 Solo Camara  6262</t>
+        </is>
+      </c>
+      <c r="C3411" t="n">
+        <v>130300.8</v>
+      </c>
+      <c r="D3411" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3412">
+      <c r="A3412" t="inlineStr">
+        <is>
+          <t>782115</t>
+        </is>
+      </c>
+      <c r="B3412" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3412" t="n">
+        <v>78933.12</v>
+      </c>
+      <c r="D3412" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3413">
+      <c r="A3413" t="inlineStr">
+        <is>
+          <t>936428</t>
+        </is>
+      </c>
+      <c r="B3413" t="inlineStr">
+        <is>
+          <t>Cristal fte.Artcool H126EFT-AEB72946002-</t>
+        </is>
+      </c>
+      <c r="C3413" t="n">
+        <v>172778.75</v>
+      </c>
+      <c r="D3413" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3414">
+      <c r="A3414" t="inlineStr">
+        <is>
+          <t>917997</t>
+        </is>
+      </c>
+      <c r="B3414" t="inlineStr">
+        <is>
+          <t>Pala Met.D700 G.Ho.Ej 3/4-12200104000162</t>
+        </is>
+      </c>
+      <c r="C3414" t="n">
+        <v>221710.8</v>
+      </c>
+      <c r="D3414" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917997</t>
+        </is>
+      </c>
+    </row>
+    <row r="3415">
+      <c r="A3415" t="inlineStr">
+        <is>
+          <t>115101</t>
+        </is>
+      </c>
+      <c r="B3415" t="inlineStr">
+        <is>
+          <t>Manovac.N.FIMA MGS10/A/63-30-0-450-BG-In</t>
+        </is>
+      </c>
+      <c r="C3415" t="n">
+        <v>22305.06</v>
+      </c>
+      <c r="D3415" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3416">
+      <c r="A3416" t="inlineStr">
+        <is>
+          <t>255302</t>
+        </is>
+      </c>
+      <c r="B3416" t="inlineStr">
+        <is>
+          <t>HELADERA PHILCO 161L PLATA  PHSD179PD A</t>
+        </is>
+      </c>
+      <c r="C3416" t="n">
+        <v>418794.38</v>
+      </c>
+      <c r="D3416" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3417">
+      <c r="A3417" t="inlineStr">
+        <is>
+          <t>999147</t>
+        </is>
+      </c>
+      <c r="B3417" t="inlineStr">
+        <is>
+          <t>TA-RSJ15190 Termo S:0002 Faltantes------</t>
+        </is>
+      </c>
+      <c r="C3417" t="n">
+        <v>1023792</v>
+      </c>
+      <c r="D3417" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999147</t>
+        </is>
+      </c>
+    </row>
+    <row r="3418">
+      <c r="A3418" t="inlineStr">
+        <is>
+          <t>942800</t>
+        </is>
+      </c>
+      <c r="B3418" t="inlineStr">
+        <is>
+          <t>C. Remoto 810900604 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3418" t="n">
+        <v>8642.4</v>
+      </c>
+      <c r="D3418" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3419">
+      <c r="A3419" t="inlineStr">
+        <is>
+          <t>936767</t>
+        </is>
+      </c>
+      <c r="B3419" t="inlineStr">
+        <is>
+          <t>Motor DC Evp.4681A20168B (ARNU09/12GTE)-</t>
+        </is>
+      </c>
+      <c r="C3419" t="n">
+        <v>155036.9</v>
+      </c>
+      <c r="D3419" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3420">
+      <c r="A3420" t="inlineStr">
+        <is>
+          <t>937114</t>
+        </is>
+      </c>
+      <c r="B3420" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Option EBR57726712</t>
+        </is>
+      </c>
+      <c r="C3420" t="n">
+        <v>6897.3</v>
+      </c>
+      <c r="D3420" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3421">
+      <c r="A3421" t="inlineStr">
+        <is>
+          <t>470157</t>
+        </is>
+      </c>
+      <c r="B3421" t="inlineStr">
+        <is>
+          <t>Codo 5/16FMx1/4FM----de bronce-HEA82----</t>
+        </is>
+      </c>
+      <c r="C3421" t="n">
+        <v>9999.700000000001</v>
+      </c>
+      <c r="D3421" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/470157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3422">
+      <c r="A3422" t="inlineStr">
+        <is>
+          <t>961375</t>
+        </is>
+      </c>
+      <c r="B3422" t="inlineStr">
+        <is>
+          <t>Mot.MANEUROP-NTZ215A4LR-7.3-R404-3Fc/vis</t>
+        </is>
+      </c>
+      <c r="C3422" t="n">
+        <v>5143308.3</v>
+      </c>
+      <c r="D3422" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961375</t>
+        </is>
+      </c>
+    </row>
+    <row r="3423">
+      <c r="A3423" t="inlineStr">
+        <is>
+          <t>938700</t>
+        </is>
+      </c>
+      <c r="B3423" t="inlineStr">
+        <is>
+          <t>Ctrl Alambrico KJRH-90B 17317100A30104--</t>
+        </is>
+      </c>
+      <c r="C3423" t="n">
+        <v>246502.3</v>
+      </c>
+      <c r="D3423" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3424">
+      <c r="A3424" t="inlineStr">
+        <is>
+          <t>911150</t>
+        </is>
+      </c>
+      <c r="B3424" t="inlineStr">
+        <is>
+          <t>Kit Soporte Auxiliar p/inst. U.Evap-----</t>
+        </is>
+      </c>
+      <c r="C3424" t="n">
+        <v>29846.75</v>
+      </c>
+      <c r="D3424" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3425">
+      <c r="A3425" t="inlineStr">
+        <is>
+          <t>942200</t>
+        </is>
+      </c>
+      <c r="B3425" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3425" t="n">
+        <v>358931.86</v>
+      </c>
+      <c r="D3425" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3426">
+      <c r="A3426" t="inlineStr">
+        <is>
+          <t>936253</t>
+        </is>
+      </c>
+      <c r="B3426" t="inlineStr">
+        <is>
+          <t>U.Ext."LG"A4UW24GFA4 Index:39 220-1-50Hz</t>
+        </is>
+      </c>
+      <c r="C3426" t="n">
+        <v>1798782.6</v>
+      </c>
+      <c r="D3426" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936253</t>
+        </is>
+      </c>
+    </row>
+    <row r="3427">
+      <c r="A3427" t="inlineStr">
+        <is>
+          <t>908010</t>
+        </is>
+      </c>
+      <c r="B3427" t="inlineStr">
+        <is>
+          <t>U.C. "TADIRAN" Mini VRF PRIME OM12IL</t>
+        </is>
+      </c>
+      <c r="C3427" t="n">
+        <v>4444188</v>
+      </c>
+      <c r="D3427" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3428">
+      <c r="A3428" t="inlineStr">
+        <is>
+          <t>938300</t>
+        </is>
+      </c>
+      <c r="B3428" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 35kW 380 TC-SS35</t>
+        </is>
+      </c>
+      <c r="C3428" t="n">
+        <v>7394736.6</v>
+      </c>
+      <c r="D3428" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3429">
+      <c r="A3429" t="inlineStr">
+        <is>
+          <t>910613</t>
+        </is>
+      </c>
+      <c r="B3429" t="inlineStr">
+        <is>
+          <t>Anillo Plástico Difusor Fan 22"0161L0000</t>
+        </is>
+      </c>
+      <c r="C3429" t="n">
+        <v>44056.85</v>
+      </c>
+      <c r="D3429" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3430">
+      <c r="A3430" t="inlineStr">
+        <is>
+          <t>908904</t>
+        </is>
+      </c>
+      <c r="B3430" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20A (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3430" t="n">
+        <v>199717</v>
+      </c>
+      <c r="D3430" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908904</t>
+        </is>
+      </c>
+    </row>
+    <row r="3431">
+      <c r="A3431" t="inlineStr">
+        <is>
+          <t>917881</t>
+        </is>
+      </c>
+      <c r="B3431" t="inlineStr">
+        <is>
+          <t>Filt.Aire Der.325x290p/9/12 201132590112</t>
+        </is>
+      </c>
+      <c r="C3431" t="n">
+        <v>6343.3</v>
+      </c>
+      <c r="D3431" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917881</t>
+        </is>
+      </c>
+    </row>
+    <row r="3432">
+      <c r="A3432" t="inlineStr">
+        <is>
+          <t>999863</t>
+        </is>
+      </c>
+      <c r="B3432" t="inlineStr">
+        <is>
+          <t>E26TFI Evap.Inver.2600fg. 0635 Viejo Mod</t>
+        </is>
+      </c>
+      <c r="C3432" t="n">
+        <v>75550.44</v>
+      </c>
+      <c r="D3432" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999863</t>
+        </is>
+      </c>
+    </row>
+    <row r="3433">
+      <c r="A3433" t="inlineStr">
+        <is>
+          <t>917544</t>
+        </is>
+      </c>
+      <c r="B3433" t="inlineStr">
+        <is>
+          <t>Motor Evp.35WC -RPG20D---202400300215---</t>
+        </is>
+      </c>
+      <c r="C3433" t="n">
+        <v>38987.75</v>
+      </c>
+      <c r="D3433" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3434">
+      <c r="A3434" t="inlineStr">
+        <is>
+          <t>937181</t>
+        </is>
+      </c>
+      <c r="B3434" t="inlineStr">
+        <is>
+          <t>PCB Main S4UW18KL3AA/KLRPA EBR82278538</t>
+        </is>
+      </c>
+      <c r="C3434" t="n">
+        <v>230200.85</v>
+      </c>
+      <c r="D3434" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937181</t>
+        </is>
+      </c>
+    </row>
+    <row r="3435">
+      <c r="A3435" t="inlineStr">
+        <is>
+          <t>999589</t>
+        </is>
+      </c>
+      <c r="B3435" t="inlineStr">
+        <is>
+          <t>Calefact.GOODMAN GMP75 Solo Camara  6262</t>
+        </is>
+      </c>
+      <c r="C3435" t="n">
+        <v>130300.8</v>
+      </c>
+      <c r="D3435" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3436">
+      <c r="A3436" t="inlineStr">
+        <is>
+          <t>782115</t>
+        </is>
+      </c>
+      <c r="B3436" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3436" t="n">
+        <v>78933.12</v>
+      </c>
+      <c r="D3436" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3437">
+      <c r="A3437" t="inlineStr">
+        <is>
+          <t>936428</t>
+        </is>
+      </c>
+      <c r="B3437" t="inlineStr">
+        <is>
+          <t>Cristal fte.Artcool H126EFT-AEB72946002-</t>
+        </is>
+      </c>
+      <c r="C3437" t="n">
+        <v>172778.75</v>
+      </c>
+      <c r="D3437" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3438">
+      <c r="A3438" t="inlineStr">
+        <is>
+          <t>917997</t>
+        </is>
+      </c>
+      <c r="B3438" t="inlineStr">
+        <is>
+          <t>Pala Met.D700 G.Ho.Ej 3/4-12200104000162</t>
+        </is>
+      </c>
+      <c r="C3438" t="n">
+        <v>221710.8</v>
+      </c>
+      <c r="D3438" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917997</t>
+        </is>
+      </c>
+    </row>
+    <row r="3439">
+      <c r="A3439" t="inlineStr">
+        <is>
+          <t>115101</t>
+        </is>
+      </c>
+      <c r="B3439" t="inlineStr">
+        <is>
+          <t>Manovac.N.FIMA MGS10/A/63-30-0-450-BG-In</t>
+        </is>
+      </c>
+      <c r="C3439" t="n">
+        <v>22305.06</v>
+      </c>
+      <c r="D3439" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3440">
+      <c r="A3440" t="inlineStr">
+        <is>
+          <t>255302</t>
+        </is>
+      </c>
+      <c r="B3440" t="inlineStr">
+        <is>
+          <t>HELADERA PHILCO 161L PLATA  PHSD179PD A</t>
+        </is>
+      </c>
+      <c r="C3440" t="n">
+        <v>418794.38</v>
+      </c>
+      <c r="D3440" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3441">
+      <c r="A3441" t="inlineStr">
+        <is>
+          <t>999147</t>
+        </is>
+      </c>
+      <c r="B3441" t="inlineStr">
+        <is>
+          <t>TA-RSJ15190 Termo S:0002 Faltantes------</t>
+        </is>
+      </c>
+      <c r="C3441" t="n">
+        <v>1023792</v>
+      </c>
+      <c r="D3441" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999147</t>
+        </is>
+      </c>
+    </row>
+    <row r="3442">
+      <c r="A3442" t="inlineStr">
+        <is>
+          <t>942800</t>
+        </is>
+      </c>
+      <c r="B3442" t="inlineStr">
+        <is>
+          <t>C. Remoto 810900604 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3442" t="n">
+        <v>8642.4</v>
+      </c>
+      <c r="D3442" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3443">
+      <c r="A3443" t="inlineStr">
+        <is>
+          <t>936767</t>
+        </is>
+      </c>
+      <c r="B3443" t="inlineStr">
+        <is>
+          <t>Motor DC Evp.4681A20168B (ARNU09/12GTE)-</t>
+        </is>
+      </c>
+      <c r="C3443" t="n">
+        <v>155036.9</v>
+      </c>
+      <c r="D3443" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3444">
+      <c r="A3444" t="inlineStr">
+        <is>
+          <t>937114</t>
+        </is>
+      </c>
+      <c r="B3444" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Option EBR57726712</t>
+        </is>
+      </c>
+      <c r="C3444" t="n">
+        <v>6897.3</v>
+      </c>
+      <c r="D3444" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3445">
+      <c r="A3445" t="inlineStr">
+        <is>
+          <t>470157</t>
+        </is>
+      </c>
+      <c r="B3445" t="inlineStr">
+        <is>
+          <t>Codo 5/16FMx1/4FM----de bronce-HEA82----</t>
+        </is>
+      </c>
+      <c r="C3445" t="n">
+        <v>9999.700000000001</v>
+      </c>
+      <c r="D3445" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/470157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3446">
+      <c r="A3446" t="inlineStr">
+        <is>
+          <t>961375</t>
+        </is>
+      </c>
+      <c r="B3446" t="inlineStr">
+        <is>
+          <t>Mot.MANEUROP-NTZ215A4LR-7.3-R404-3Fc/vis</t>
+        </is>
+      </c>
+      <c r="C3446" t="n">
+        <v>5143308.3</v>
+      </c>
+      <c r="D3446" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961375</t>
+        </is>
+      </c>
+    </row>
+    <row r="3447">
+      <c r="A3447" t="inlineStr">
+        <is>
+          <t>938700</t>
+        </is>
+      </c>
+      <c r="B3447" t="inlineStr">
+        <is>
+          <t>Ctrl Alambrico KJRH-90B 17317100A30104--</t>
+        </is>
+      </c>
+      <c r="C3447" t="n">
+        <v>246502.3</v>
+      </c>
+      <c r="D3447" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3448">
+      <c r="A3448" t="inlineStr">
+        <is>
+          <t>911150</t>
+        </is>
+      </c>
+      <c r="B3448" t="inlineStr">
+        <is>
+          <t>Kit Soporte Auxiliar p/inst. U.Evap-----</t>
+        </is>
+      </c>
+      <c r="C3448" t="n">
+        <v>29846.75</v>
+      </c>
+      <c r="D3448" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3449">
+      <c r="A3449" t="inlineStr">
+        <is>
+          <t>942200</t>
+        </is>
+      </c>
+      <c r="B3449" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3449" t="n">
+        <v>358931.86</v>
+      </c>
+      <c r="D3449" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3450">
+      <c r="A3450" t="inlineStr">
+        <is>
+          <t>936253</t>
+        </is>
+      </c>
+      <c r="B3450" t="inlineStr">
+        <is>
+          <t>U.Ext."LG"A4UW24GFA4 Index:39 220-1-50Hz</t>
+        </is>
+      </c>
+      <c r="C3450" t="n">
+        <v>1798782.6</v>
+      </c>
+      <c r="D3450" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936253</t>
+        </is>
+      </c>
+    </row>
+    <row r="3451">
+      <c r="A3451" t="inlineStr">
+        <is>
+          <t>908010</t>
+        </is>
+      </c>
+      <c r="B3451" t="inlineStr">
+        <is>
+          <t>U.C. "TADIRAN" Mini VRF PRIME OM12IL</t>
+        </is>
+      </c>
+      <c r="C3451" t="n">
+        <v>4444188</v>
+      </c>
+      <c r="D3451" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3452">
+      <c r="A3452" t="inlineStr">
+        <is>
+          <t>938300</t>
+        </is>
+      </c>
+      <c r="B3452" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 35kW 380 TC-SS35</t>
+        </is>
+      </c>
+      <c r="C3452" t="n">
+        <v>7394736.6</v>
+      </c>
+      <c r="D3452" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3453">
+      <c r="A3453" t="inlineStr">
+        <is>
+          <t>910613</t>
+        </is>
+      </c>
+      <c r="B3453" t="inlineStr">
+        <is>
+          <t>Anillo Plástico Difusor Fan 22"0161L0000</t>
+        </is>
+      </c>
+      <c r="C3453" t="n">
+        <v>44056.85</v>
+      </c>
+      <c r="D3453" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3454">
+      <c r="A3454" t="inlineStr">
+        <is>
+          <t>908904</t>
+        </is>
+      </c>
+      <c r="B3454" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20A (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3454" t="n">
+        <v>199717</v>
+      </c>
+      <c r="D3454" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908904</t>
+        </is>
+      </c>
+    </row>
+    <row r="3455">
+      <c r="A3455" t="inlineStr">
+        <is>
+          <t>917881</t>
+        </is>
+      </c>
+      <c r="B3455" t="inlineStr">
+        <is>
+          <t>Filt.Aire Der.325x290p/9/12 201132590112</t>
+        </is>
+      </c>
+      <c r="C3455" t="n">
+        <v>6343.3</v>
+      </c>
+      <c r="D3455" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917881</t>
+        </is>
+      </c>
+    </row>
+    <row r="3456">
+      <c r="A3456" t="inlineStr">
+        <is>
+          <t>999863</t>
+        </is>
+      </c>
+      <c r="B3456" t="inlineStr">
+        <is>
+          <t>E26TFI Evap.Inver.2600fg. 0635 Viejo Mod</t>
+        </is>
+      </c>
+      <c r="C3456" t="n">
+        <v>75550.44</v>
+      </c>
+      <c r="D3456" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999863</t>
+        </is>
+      </c>
+    </row>
+    <row r="3457">
+      <c r="A3457" t="inlineStr">
+        <is>
+          <t>917544</t>
+        </is>
+      </c>
+      <c r="B3457" t="inlineStr">
+        <is>
+          <t>Motor Evp.35WC -RPG20D---202400300215---</t>
+        </is>
+      </c>
+      <c r="C3457" t="n">
+        <v>38987.75</v>
+      </c>
+      <c r="D3457" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3458">
+      <c r="A3458" t="inlineStr">
+        <is>
+          <t>937181</t>
+        </is>
+      </c>
+      <c r="B3458" t="inlineStr">
+        <is>
+          <t>PCB Main S4UW18KL3AA/KLRPA EBR82278538</t>
+        </is>
+      </c>
+      <c r="C3458" t="n">
+        <v>230200.85</v>
+      </c>
+      <c r="D3458" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937181</t>
+        </is>
+      </c>
+    </row>
+    <row r="3459">
+      <c r="A3459" t="inlineStr">
+        <is>
+          <t>999589</t>
+        </is>
+      </c>
+      <c r="B3459" t="inlineStr">
+        <is>
+          <t>Calefact.GOODMAN GMP75 Solo Camara  6262</t>
+        </is>
+      </c>
+      <c r="C3459" t="n">
+        <v>130300.8</v>
+      </c>
+      <c r="D3459" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3460">
+      <c r="A3460" t="inlineStr">
+        <is>
+          <t>782115</t>
+        </is>
+      </c>
+      <c r="B3460" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3460" t="n">
+        <v>78933.12</v>
+      </c>
+      <c r="D3460" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3461">
+      <c r="A3461" t="inlineStr">
+        <is>
+          <t>936428</t>
+        </is>
+      </c>
+      <c r="B3461" t="inlineStr">
+        <is>
+          <t>Cristal fte.Artcool H126EFT-AEB72946002-</t>
+        </is>
+      </c>
+      <c r="C3461" t="n">
+        <v>172778.75</v>
+      </c>
+      <c r="D3461" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3462">
+      <c r="A3462" t="inlineStr">
+        <is>
+          <t>917997</t>
+        </is>
+      </c>
+      <c r="B3462" t="inlineStr">
+        <is>
+          <t>Pala Met.D700 G.Ho.Ej 3/4-12200104000162</t>
+        </is>
+      </c>
+      <c r="C3462" t="n">
+        <v>221710.8</v>
+      </c>
+      <c r="D3462" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917997</t>
+        </is>
+      </c>
+    </row>
+    <row r="3463">
+      <c r="A3463" t="inlineStr">
+        <is>
+          <t>115101</t>
+        </is>
+      </c>
+      <c r="B3463" t="inlineStr">
+        <is>
+          <t>Manovac.N.FIMA MGS10/A/63-30-0-450-BG-In</t>
+        </is>
+      </c>
+      <c r="C3463" t="n">
+        <v>22305.06</v>
+      </c>
+      <c r="D3463" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3464">
+      <c r="A3464" t="inlineStr">
+        <is>
+          <t>255302</t>
+        </is>
+      </c>
+      <c r="B3464" t="inlineStr">
+        <is>
+          <t>HELADERA PHILCO 161L PLATA  PHSD179PD A</t>
+        </is>
+      </c>
+      <c r="C3464" t="n">
+        <v>418794.38</v>
+      </c>
+      <c r="D3464" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3465">
+      <c r="A3465" t="inlineStr">
+        <is>
+          <t>999147</t>
+        </is>
+      </c>
+      <c r="B3465" t="inlineStr">
+        <is>
+          <t>TA-RSJ15190 Termo S:0002 Faltantes------</t>
+        </is>
+      </c>
+      <c r="C3465" t="n">
+        <v>1023792</v>
+      </c>
+      <c r="D3465" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999147</t>
+        </is>
+      </c>
+    </row>
+    <row r="3466">
+      <c r="A3466" t="inlineStr">
+        <is>
+          <t>942800</t>
+        </is>
+      </c>
+      <c r="B3466" t="inlineStr">
+        <is>
+          <t>C. Remoto 810900604 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3466" t="n">
+        <v>8642.4</v>
+      </c>
+      <c r="D3466" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3467">
+      <c r="A3467" t="inlineStr">
+        <is>
+          <t>936767</t>
+        </is>
+      </c>
+      <c r="B3467" t="inlineStr">
+        <is>
+          <t>Motor DC Evp.4681A20168B (ARNU09/12GTE)-</t>
+        </is>
+      </c>
+      <c r="C3467" t="n">
+        <v>155036.9</v>
+      </c>
+      <c r="D3467" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3468">
+      <c r="A3468" t="inlineStr">
+        <is>
+          <t>937114</t>
+        </is>
+      </c>
+      <c r="B3468" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Option EBR57726712</t>
+        </is>
+      </c>
+      <c r="C3468" t="n">
+        <v>6897.3</v>
+      </c>
+      <c r="D3468" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3469">
+      <c r="A3469" t="inlineStr">
+        <is>
+          <t>470157</t>
+        </is>
+      </c>
+      <c r="B3469" t="inlineStr">
+        <is>
+          <t>Codo 5/16FMx1/4FM----de bronce-HEA82----</t>
+        </is>
+      </c>
+      <c r="C3469" t="n">
+        <v>9999.700000000001</v>
+      </c>
+      <c r="D3469" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/470157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3470">
+      <c r="A3470" t="inlineStr">
+        <is>
+          <t>961375</t>
+        </is>
+      </c>
+      <c r="B3470" t="inlineStr">
+        <is>
+          <t>Mot.MANEUROP-NTZ215A4LR-7.3-R404-3Fc/vis</t>
+        </is>
+      </c>
+      <c r="C3470" t="n">
+        <v>5143308.3</v>
+      </c>
+      <c r="D3470" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961375</t>
+        </is>
+      </c>
+    </row>
+    <row r="3471">
+      <c r="A3471" t="inlineStr">
+        <is>
+          <t>938700</t>
+        </is>
+      </c>
+      <c r="B3471" t="inlineStr">
+        <is>
+          <t>Ctrl Alambrico KJRH-90B 17317100A30104--</t>
+        </is>
+      </c>
+      <c r="C3471" t="n">
+        <v>246502.3</v>
+      </c>
+      <c r="D3471" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3472">
+      <c r="A3472" t="inlineStr">
+        <is>
+          <t>911150</t>
+        </is>
+      </c>
+      <c r="B3472" t="inlineStr">
+        <is>
+          <t>Kit Soporte Auxiliar p/inst. U.Evap-----</t>
+        </is>
+      </c>
+      <c r="C3472" t="n">
+        <v>29846.75</v>
+      </c>
+      <c r="D3472" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3473">
+      <c r="A3473" t="inlineStr">
+        <is>
+          <t>942200</t>
+        </is>
+      </c>
+      <c r="B3473" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3473" t="n">
+        <v>358931.86</v>
+      </c>
+      <c r="D3473" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3474">
+      <c r="A3474" t="inlineStr">
+        <is>
+          <t>936253</t>
+        </is>
+      </c>
+      <c r="B3474" t="inlineStr">
+        <is>
+          <t>U.Ext."LG"A4UW24GFA4 Index:39 220-1-50Hz</t>
+        </is>
+      </c>
+      <c r="C3474" t="n">
+        <v>1798782.6</v>
+      </c>
+      <c r="D3474" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936253</t>
+        </is>
+      </c>
+    </row>
+    <row r="3475">
+      <c r="A3475" t="inlineStr">
+        <is>
+          <t>908010</t>
+        </is>
+      </c>
+      <c r="B3475" t="inlineStr">
+        <is>
+          <t>U.C. "TADIRAN" Mini VRF PRIME OM12IL</t>
+        </is>
+      </c>
+      <c r="C3475" t="n">
+        <v>4444188</v>
+      </c>
+      <c r="D3475" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3476">
+      <c r="A3476" t="inlineStr">
+        <is>
+          <t>938300</t>
+        </is>
+      </c>
+      <c r="B3476" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 35kW 380 TC-SS35</t>
+        </is>
+      </c>
+      <c r="C3476" t="n">
+        <v>7394736.6</v>
+      </c>
+      <c r="D3476" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3477">
+      <c r="A3477" t="inlineStr">
+        <is>
+          <t>910613</t>
+        </is>
+      </c>
+      <c r="B3477" t="inlineStr">
+        <is>
+          <t>Anillo Plástico Difusor Fan 22"0161L0000</t>
+        </is>
+      </c>
+      <c r="C3477" t="n">
+        <v>44056.85</v>
+      </c>
+      <c r="D3477" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="inlineStr">
+        <is>
+          <t>908904</t>
+        </is>
+      </c>
+      <c r="B3478" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20A (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3478" t="n">
+        <v>199717</v>
+      </c>
+      <c r="D3478" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908904</t>
+        </is>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="inlineStr">
+        <is>
+          <t>917881</t>
+        </is>
+      </c>
+      <c r="B3479" t="inlineStr">
+        <is>
+          <t>Filt.Aire Der.325x290p/9/12 201132590112</t>
+        </is>
+      </c>
+      <c r="C3479" t="n">
+        <v>6343.3</v>
+      </c>
+      <c r="D3479" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917881</t>
+        </is>
+      </c>
+    </row>
+    <row r="3480">
+      <c r="A3480" t="inlineStr">
+        <is>
+          <t>999863</t>
+        </is>
+      </c>
+      <c r="B3480" t="inlineStr">
+        <is>
+          <t>E26TFI Evap.Inver.2600fg. 0635 Viejo Mod</t>
+        </is>
+      </c>
+      <c r="C3480" t="n">
+        <v>75550.44</v>
+      </c>
+      <c r="D3480" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999863</t>
+        </is>
+      </c>
+    </row>
+    <row r="3481">
+      <c r="A3481" t="inlineStr">
+        <is>
+          <t>917544</t>
+        </is>
+      </c>
+      <c r="B3481" t="inlineStr">
+        <is>
+          <t>Motor Evp.35WC -RPG20D---202400300215---</t>
+        </is>
+      </c>
+      <c r="C3481" t="n">
+        <v>38987.75</v>
+      </c>
+      <c r="D3481" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3482">
+      <c r="A3482" t="inlineStr">
+        <is>
+          <t>937181</t>
+        </is>
+      </c>
+      <c r="B3482" t="inlineStr">
+        <is>
+          <t>PCB Main S4UW18KL3AA/KLRPA EBR82278538</t>
+        </is>
+      </c>
+      <c r="C3482" t="n">
+        <v>230200.85</v>
+      </c>
+      <c r="D3482" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937181</t>
+        </is>
+      </c>
+    </row>
+    <row r="3483">
+      <c r="A3483" t="inlineStr">
+        <is>
+          <t>999589</t>
+        </is>
+      </c>
+      <c r="B3483" t="inlineStr">
+        <is>
+          <t>Calefact.GOODMAN GMP75 Solo Camara  6262</t>
+        </is>
+      </c>
+      <c r="C3483" t="n">
+        <v>130300.8</v>
+      </c>
+      <c r="D3483" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3484">
+      <c r="A3484" t="inlineStr">
+        <is>
+          <t>782115</t>
+        </is>
+      </c>
+      <c r="B3484" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3484" t="n">
+        <v>78933.12</v>
+      </c>
+      <c r="D3484" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3485">
+      <c r="A3485" t="inlineStr">
+        <is>
+          <t>936428</t>
+        </is>
+      </c>
+      <c r="B3485" t="inlineStr">
+        <is>
+          <t>Cristal fte.Artcool H126EFT-AEB72946002-</t>
+        </is>
+      </c>
+      <c r="C3485" t="n">
+        <v>172778.75</v>
+      </c>
+      <c r="D3485" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3486">
+      <c r="A3486" t="inlineStr">
+        <is>
+          <t>917997</t>
+        </is>
+      </c>
+      <c r="B3486" t="inlineStr">
+        <is>
+          <t>Pala Met.D700 G.Ho.Ej 3/4-12200104000162</t>
+        </is>
+      </c>
+      <c r="C3486" t="n">
+        <v>221710.8</v>
+      </c>
+      <c r="D3486" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917997</t>
+        </is>
+      </c>
+    </row>
+    <row r="3487">
+      <c r="A3487" t="inlineStr">
+        <is>
+          <t>115101</t>
+        </is>
+      </c>
+      <c r="B3487" t="inlineStr">
+        <is>
+          <t>Manovac.N.FIMA MGS10/A/63-30-0-450-BG-In</t>
+        </is>
+      </c>
+      <c r="C3487" t="n">
+        <v>22305.06</v>
+      </c>
+      <c r="D3487" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3488">
+      <c r="A3488" t="inlineStr">
+        <is>
+          <t>255302</t>
+        </is>
+      </c>
+      <c r="B3488" t="inlineStr">
+        <is>
+          <t>HELADERA PHILCO 161L PLATA  PHSD179PD A</t>
+        </is>
+      </c>
+      <c r="C3488" t="n">
+        <v>418794.38</v>
+      </c>
+      <c r="D3488" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3489">
+      <c r="A3489" t="inlineStr">
+        <is>
+          <t>999147</t>
+        </is>
+      </c>
+      <c r="B3489" t="inlineStr">
+        <is>
+          <t>TA-RSJ15190 Termo S:0002 Faltantes------</t>
+        </is>
+      </c>
+      <c r="C3489" t="n">
+        <v>1023792</v>
+      </c>
+      <c r="D3489" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999147</t>
+        </is>
+      </c>
+    </row>
+    <row r="3490">
+      <c r="A3490" t="inlineStr">
+        <is>
+          <t>942800</t>
+        </is>
+      </c>
+      <c r="B3490" t="inlineStr">
+        <is>
+          <t>C. Remoto 810900604 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3490" t="n">
+        <v>8642.4</v>
+      </c>
+      <c r="D3490" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3491">
+      <c r="A3491" t="inlineStr">
+        <is>
+          <t>936767</t>
+        </is>
+      </c>
+      <c r="B3491" t="inlineStr">
+        <is>
+          <t>Motor DC Evp.4681A20168B (ARNU09/12GTE)-</t>
+        </is>
+      </c>
+      <c r="C3491" t="n">
+        <v>155036.9</v>
+      </c>
+      <c r="D3491" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3492">
+      <c r="A3492" t="inlineStr">
+        <is>
+          <t>937114</t>
+        </is>
+      </c>
+      <c r="B3492" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Option EBR57726712</t>
+        </is>
+      </c>
+      <c r="C3492" t="n">
+        <v>6897.3</v>
+      </c>
+      <c r="D3492" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3493">
+      <c r="A3493" t="inlineStr">
+        <is>
+          <t>470157</t>
+        </is>
+      </c>
+      <c r="B3493" t="inlineStr">
+        <is>
+          <t>Codo 5/16FMx1/4FM----de bronce-HEA82----</t>
+        </is>
+      </c>
+      <c r="C3493" t="n">
+        <v>9999.700000000001</v>
+      </c>
+      <c r="D3493" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/470157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3494">
+      <c r="A3494" t="inlineStr">
+        <is>
+          <t>961375</t>
+        </is>
+      </c>
+      <c r="B3494" t="inlineStr">
+        <is>
+          <t>Mot.MANEUROP-NTZ215A4LR-7.3-R404-3Fc/vis</t>
+        </is>
+      </c>
+      <c r="C3494" t="n">
+        <v>5143308.3</v>
+      </c>
+      <c r="D3494" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961375</t>
+        </is>
+      </c>
+    </row>
+    <row r="3495">
+      <c r="A3495" t="inlineStr">
+        <is>
+          <t>938700</t>
+        </is>
+      </c>
+      <c r="B3495" t="inlineStr">
+        <is>
+          <t>Ctrl Alambrico KJRH-90B 17317100A30104--</t>
+        </is>
+      </c>
+      <c r="C3495" t="n">
+        <v>246502.3</v>
+      </c>
+      <c r="D3495" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3496">
+      <c r="A3496" t="inlineStr">
+        <is>
+          <t>911150</t>
+        </is>
+      </c>
+      <c r="B3496" t="inlineStr">
+        <is>
+          <t>Kit Soporte Auxiliar p/inst. U.Evap-----</t>
+        </is>
+      </c>
+      <c r="C3496" t="n">
+        <v>29846.75</v>
+      </c>
+      <c r="D3496" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3497">
+      <c r="A3497" t="inlineStr">
+        <is>
+          <t>942200</t>
+        </is>
+      </c>
+      <c r="B3497" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3497" t="n">
+        <v>358931.86</v>
+      </c>
+      <c r="D3497" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3498">
+      <c r="A3498" t="inlineStr">
+        <is>
+          <t>936253</t>
+        </is>
+      </c>
+      <c r="B3498" t="inlineStr">
+        <is>
+          <t>U.Ext."LG"A4UW24GFA4 Index:39 220-1-50Hz</t>
+        </is>
+      </c>
+      <c r="C3498" t="n">
+        <v>1798782.6</v>
+      </c>
+      <c r="D3498" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936253</t>
+        </is>
+      </c>
+    </row>
+    <row r="3499">
+      <c r="A3499" t="inlineStr">
+        <is>
+          <t>908010</t>
+        </is>
+      </c>
+      <c r="B3499" t="inlineStr">
+        <is>
+          <t>U.C. "TADIRAN" Mini VRF PRIME OM12IL</t>
+        </is>
+      </c>
+      <c r="C3499" t="n">
+        <v>4444188</v>
+      </c>
+      <c r="D3499" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3500">
+      <c r="A3500" t="inlineStr">
+        <is>
+          <t>938300</t>
+        </is>
+      </c>
+      <c r="B3500" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 35kW 380 TC-SS35</t>
+        </is>
+      </c>
+      <c r="C3500" t="n">
+        <v>7394736.6</v>
+      </c>
+      <c r="D3500" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3501">
+      <c r="A3501" t="inlineStr">
+        <is>
+          <t>910613</t>
+        </is>
+      </c>
+      <c r="B3501" t="inlineStr">
+        <is>
+          <t>Anillo Plástico Difusor Fan 22"0161L0000</t>
+        </is>
+      </c>
+      <c r="C3501" t="n">
+        <v>44056.85</v>
+      </c>
+      <c r="D3501" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3502">
+      <c r="A3502" t="inlineStr">
+        <is>
+          <t>908904</t>
+        </is>
+      </c>
+      <c r="B3502" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20A (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3502" t="n">
+        <v>199717</v>
+      </c>
+      <c r="D3502" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908904</t>
+        </is>
+      </c>
+    </row>
+    <row r="3503">
+      <c r="A3503" t="inlineStr">
+        <is>
+          <t>917881</t>
+        </is>
+      </c>
+      <c r="B3503" t="inlineStr">
+        <is>
+          <t>Filt.Aire Der.325x290p/9/12 201132590112</t>
+        </is>
+      </c>
+      <c r="C3503" t="n">
+        <v>6343.3</v>
+      </c>
+      <c r="D3503" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917881</t>
+        </is>
+      </c>
+    </row>
+    <row r="3504">
+      <c r="A3504" t="inlineStr">
+        <is>
+          <t>999863</t>
+        </is>
+      </c>
+      <c r="B3504" t="inlineStr">
+        <is>
+          <t>E26TFI Evap.Inver.2600fg. 0635 Viejo Mod</t>
+        </is>
+      </c>
+      <c r="C3504" t="n">
+        <v>75550.44</v>
+      </c>
+      <c r="D3504" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999863</t>
+        </is>
+      </c>
+    </row>
+    <row r="3505">
+      <c r="A3505" t="inlineStr">
+        <is>
+          <t>917544</t>
+        </is>
+      </c>
+      <c r="B3505" t="inlineStr">
+        <is>
+          <t>Motor Evp.35WC -RPG20D---202400300215---</t>
+        </is>
+      </c>
+      <c r="C3505" t="n">
+        <v>38987.75</v>
+      </c>
+      <c r="D3505" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3506">
+      <c r="A3506" t="inlineStr">
+        <is>
+          <t>937181</t>
+        </is>
+      </c>
+      <c r="B3506" t="inlineStr">
+        <is>
+          <t>PCB Main S4UW18KL3AA/KLRPA EBR82278538</t>
+        </is>
+      </c>
+      <c r="C3506" t="n">
+        <v>230200.85</v>
+      </c>
+      <c r="D3506" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937181</t>
+        </is>
+      </c>
+    </row>
+    <row r="3507">
+      <c r="A3507" t="inlineStr">
+        <is>
+          <t>999589</t>
+        </is>
+      </c>
+      <c r="B3507" t="inlineStr">
+        <is>
+          <t>Calefact.GOODMAN GMP75 Solo Camara  6262</t>
+        </is>
+      </c>
+      <c r="C3507" t="n">
+        <v>130300.8</v>
+      </c>
+      <c r="D3507" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3508">
+      <c r="A3508" t="inlineStr">
+        <is>
+          <t>782115</t>
+        </is>
+      </c>
+      <c r="B3508" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3508" t="n">
+        <v>78933.12</v>
+      </c>
+      <c r="D3508" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3509">
+      <c r="A3509" t="inlineStr">
+        <is>
+          <t>936428</t>
+        </is>
+      </c>
+      <c r="B3509" t="inlineStr">
+        <is>
+          <t>Cristal fte.Artcool H126EFT-AEB72946002-</t>
+        </is>
+      </c>
+      <c r="C3509" t="n">
+        <v>172778.75</v>
+      </c>
+      <c r="D3509" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936428</t>
+        </is>
+      </c>
+    </row>
+    <row r="3510">
+      <c r="A3510" t="inlineStr">
+        <is>
+          <t>917997</t>
+        </is>
+      </c>
+      <c r="B3510" t="inlineStr">
+        <is>
+          <t>Pala Met.D700 G.Ho.Ej 3/4-12200104000162</t>
+        </is>
+      </c>
+      <c r="C3510" t="n">
+        <v>221710.8</v>
+      </c>
+      <c r="D3510" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917997</t>
+        </is>
+      </c>
+    </row>
+    <row r="3511">
+      <c r="A3511" t="inlineStr">
+        <is>
+          <t>115101</t>
+        </is>
+      </c>
+      <c r="B3511" t="inlineStr">
+        <is>
+          <t>Manovac.N.FIMA MGS10/A/63-30-0-450-BG-In</t>
+        </is>
+      </c>
+      <c r="C3511" t="n">
+        <v>22305.06</v>
+      </c>
+      <c r="D3511" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3512">
+      <c r="A3512" t="inlineStr">
+        <is>
+          <t>255302</t>
+        </is>
+      </c>
+      <c r="B3512" t="inlineStr">
+        <is>
+          <t>HELADERA PHILCO 161L PLATA  PHSD179PD A</t>
+        </is>
+      </c>
+      <c r="C3512" t="n">
+        <v>418794.38</v>
+      </c>
+      <c r="D3512" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3513">
+      <c r="A3513" t="inlineStr">
+        <is>
+          <t>999147</t>
+        </is>
+      </c>
+      <c r="B3513" t="inlineStr">
+        <is>
+          <t>TA-RSJ15190 Termo S:0002 Faltantes------</t>
+        </is>
+      </c>
+      <c r="C3513" t="n">
+        <v>1023792</v>
+      </c>
+      <c r="D3513" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999147</t>
+        </is>
+      </c>
+    </row>
+    <row r="3514">
+      <c r="A3514" t="inlineStr">
+        <is>
+          <t>942800</t>
+        </is>
+      </c>
+      <c r="B3514" t="inlineStr">
+        <is>
+          <t>C. Remoto 810900604 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3514" t="n">
+        <v>8642.4</v>
+      </c>
+      <c r="D3514" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3515">
+      <c r="A3515" t="inlineStr">
+        <is>
+          <t>936767</t>
+        </is>
+      </c>
+      <c r="B3515" t="inlineStr">
+        <is>
+          <t>Motor DC Evp.4681A20168B (ARNU09/12GTE)-</t>
+        </is>
+      </c>
+      <c r="C3515" t="n">
+        <v>155036.9</v>
+      </c>
+      <c r="D3515" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936767</t>
+        </is>
+      </c>
+    </row>
+    <row r="3516">
+      <c r="A3516" t="inlineStr">
+        <is>
+          <t>937114</t>
+        </is>
+      </c>
+      <c r="B3516" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Option EBR57726712</t>
+        </is>
+      </c>
+      <c r="C3516" t="n">
+        <v>6897.3</v>
+      </c>
+      <c r="D3516" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3517">
+      <c r="A3517" t="inlineStr">
+        <is>
+          <t>470157</t>
+        </is>
+      </c>
+      <c r="B3517" t="inlineStr">
+        <is>
+          <t>Codo 5/16FMx1/4FM----de bronce-HEA82----</t>
+        </is>
+      </c>
+      <c r="C3517" t="n">
+        <v>9999.700000000001</v>
+      </c>
+      <c r="D3517" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/470157</t>
+        </is>
+      </c>
+    </row>
+    <row r="3518">
+      <c r="A3518" t="inlineStr">
+        <is>
+          <t>961375</t>
+        </is>
+      </c>
+      <c r="B3518" t="inlineStr">
+        <is>
+          <t>Mot.MANEUROP-NTZ215A4LR-7.3-R404-3Fc/vis</t>
+        </is>
+      </c>
+      <c r="C3518" t="n">
+        <v>5143308.3</v>
+      </c>
+      <c r="D3518" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961375</t>
+        </is>
+      </c>
+    </row>
+    <row r="3519">
+      <c r="A3519" t="inlineStr">
+        <is>
+          <t>938700</t>
+        </is>
+      </c>
+      <c r="B3519" t="inlineStr">
+        <is>
+          <t>Ctrl Alambrico KJRH-90B 17317100A30104--</t>
+        </is>
+      </c>
+      <c r="C3519" t="n">
+        <v>246502.3</v>
+      </c>
+      <c r="D3519" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3520">
+      <c r="A3520" t="inlineStr">
+        <is>
+          <t>911150</t>
+        </is>
+      </c>
+      <c r="B3520" t="inlineStr">
+        <is>
+          <t>Kit Soporte Auxiliar p/inst. U.Evap-----</t>
+        </is>
+      </c>
+      <c r="C3520" t="n">
+        <v>29846.75</v>
+      </c>
+      <c r="D3520" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911150</t>
+        </is>
+      </c>
+    </row>
+    <row r="3521">
+      <c r="A3521" t="inlineStr">
+        <is>
+          <t>942200</t>
+        </is>
+      </c>
+      <c r="B3521" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3521" t="n">
+        <v>358931.86</v>
+      </c>
+      <c r="D3521" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3522">
+      <c r="A3522" t="inlineStr">
+        <is>
+          <t>936253</t>
+        </is>
+      </c>
+      <c r="B3522" t="inlineStr">
+        <is>
+          <t>U.Ext."LG"A4UW24GFA4 Index:39 220-1-50Hz</t>
+        </is>
+      </c>
+      <c r="C3522" t="n">
+        <v>1798782.6</v>
+      </c>
+      <c r="D3522" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936253</t>
+        </is>
+      </c>
+    </row>
+    <row r="3523">
+      <c r="A3523" t="inlineStr">
+        <is>
+          <t>908010</t>
+        </is>
+      </c>
+      <c r="B3523" t="inlineStr">
+        <is>
+          <t>U.C. "TADIRAN" Mini VRF PRIME OM12IL</t>
+        </is>
+      </c>
+      <c r="C3523" t="n">
+        <v>4444188</v>
+      </c>
+      <c r="D3523" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3524">
+      <c r="A3524" t="inlineStr">
+        <is>
+          <t>938300</t>
+        </is>
+      </c>
+      <c r="B3524" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 35kW 380 TC-SS35</t>
+        </is>
+      </c>
+      <c r="C3524" t="n">
+        <v>7394736.6</v>
+      </c>
+      <c r="D3524" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3525">
+      <c r="A3525" t="inlineStr">
+        <is>
+          <t>910613</t>
+        </is>
+      </c>
+      <c r="B3525" t="inlineStr">
+        <is>
+          <t>Anillo Plástico Difusor Fan 22"0161L0000</t>
+        </is>
+      </c>
+      <c r="C3525" t="n">
+        <v>44056.85</v>
+      </c>
+      <c r="D3525" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" t="inlineStr">
+        <is>
+          <t>908904</t>
+        </is>
+      </c>
+      <c r="B3526" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20A (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3526" t="n">
+        <v>199717</v>
+      </c>
+      <c r="D3526" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908904</t>
+        </is>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" t="inlineStr">
+        <is>
+          <t>917881</t>
+        </is>
+      </c>
+      <c r="B3527" t="inlineStr">
+        <is>
+          <t>Filt.Aire Der.325x290p/9/12 201132590112</t>
+        </is>
+      </c>
+      <c r="C3527" t="n">
+        <v>6343.3</v>
+      </c>
+      <c r="D3527" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917881</t>
+        </is>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" t="inlineStr">
+        <is>
+          <t>999863</t>
+        </is>
+      </c>
+      <c r="B3528" t="inlineStr">
+        <is>
+          <t>E26TFI Evap.Inver.2600fg. 0635 Viejo Mod</t>
+        </is>
+      </c>
+      <c r="C3528" t="n">
+        <v>75550.44</v>
+      </c>
+      <c r="D3528" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999863</t>
+        </is>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" t="inlineStr">
+        <is>
+          <t>917544</t>
+        </is>
+      </c>
+      <c r="B3529" t="inlineStr">
+        <is>
+          <t>Motor Evp.35WC -RPG20D---202400300215---</t>
+        </is>
+      </c>
+      <c r="C3529" t="n">
+        <v>38987.75</v>
+      </c>
+      <c r="D3529" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917544</t>
+        </is>
+      </c>
+    </row>
+    <row r="3530">
+      <c r="A3530" t="inlineStr">
+        <is>
+          <t>782100</t>
+        </is>
+      </c>
+      <c r="B3530" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x1.5mm---------</t>
+        </is>
+      </c>
+      <c r="C3530" t="n">
+        <v>120010.8</v>
+      </c>
+      <c r="D3530" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" t="inlineStr">
+        <is>
+          <t>999954</t>
+        </is>
+      </c>
+      <c r="B3531" t="inlineStr">
+        <is>
+          <t>U.C.TA8-3200 3000 F/C  4707 con Fuga--</t>
+        </is>
+      </c>
+      <c r="C3531" t="n">
+        <v>158596.35</v>
+      </c>
+      <c r="D3531" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999954</t>
+        </is>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" t="inlineStr">
+        <is>
+          <t>115061</t>
+        </is>
+      </c>
+      <c r="B3532" t="inlineStr">
+        <is>
+          <t>Manom.BEYCA MM234/0a5 Kg-75 Lb/63mm/inf-</t>
+        </is>
+      </c>
+      <c r="C3532" t="n">
+        <v>7482.15</v>
+      </c>
+      <c r="D3532" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115061</t>
+        </is>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" t="inlineStr">
+        <is>
+          <t>979502</t>
+        </is>
+      </c>
+      <c r="B3533" t="inlineStr">
+        <is>
+          <t>U.C. M2OE-18HFN8-Q 18000BTU R32 index:30</t>
+        </is>
+      </c>
+      <c r="C3533" t="n">
+        <v>1051741.3</v>
+      </c>
+      <c r="D3533" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979502</t>
+        </is>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" t="inlineStr">
+        <is>
+          <t>994594</t>
+        </is>
+      </c>
+      <c r="B3534" t="inlineStr">
+        <is>
+          <t>Valv.Reg.Pres.evap.SANHUA CTF16H01.-5/8-</t>
+        </is>
+      </c>
+      <c r="C3534" t="n">
+        <v>93404.39999999999</v>
+      </c>
+      <c r="D3534" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994594</t>
+        </is>
+      </c>
+    </row>
+    <row r="3535">
+      <c r="A3535" t="inlineStr">
+        <is>
+          <t>946255</t>
+        </is>
+      </c>
+      <c r="B3535" t="inlineStr">
+        <is>
+          <t>Termost.dig.progr.BlueStar HVAC10(2S)---</t>
+        </is>
+      </c>
+      <c r="C3535" t="n">
+        <v>45372.6</v>
+      </c>
+      <c r="D3535" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946255</t>
+        </is>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" t="inlineStr">
+        <is>
+          <t>942802</t>
+        </is>
+      </c>
+      <c r="B3536" t="inlineStr">
+        <is>
+          <t>PCB Display 810900559A (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3536" t="n">
+        <v>22658.6</v>
+      </c>
+      <c r="D3536" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942802</t>
+        </is>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" t="inlineStr">
+        <is>
+          <t>853002</t>
+        </is>
+      </c>
+      <c r="B3537" t="inlineStr">
+        <is>
+          <t>Control Remoto  22013-000894    TA8</t>
+        </is>
+      </c>
+      <c r="C3537" t="n">
+        <v>45137.15</v>
+      </c>
+      <c r="D3537" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/853002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" t="inlineStr">
+        <is>
+          <t>937116</t>
+        </is>
+      </c>
+      <c r="B3538" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Main EBR39319516</t>
+        </is>
+      </c>
+      <c r="C3538" t="n">
+        <v>115924.5</v>
+      </c>
+      <c r="D3538" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937116</t>
+        </is>
+      </c>
+    </row>
+    <row r="3539">
+      <c r="A3539" t="inlineStr">
+        <is>
+          <t>994801</t>
+        </is>
+      </c>
+      <c r="B3539" t="inlineStr">
+        <is>
+          <t>Regulador pres.succ.SANHUA XTF15H01-5/8S</t>
+        </is>
+      </c>
+      <c r="C3539" t="n">
+        <v>80980.95</v>
+      </c>
+      <c r="D3539" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994801</t>
+        </is>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" t="inlineStr">
+        <is>
+          <t>942201</t>
+        </is>
+      </c>
+      <c r="B3540" t="inlineStr">
+        <is>
+          <t>UE."TCL" ONOFF TACA-2650W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3540" t="n">
+        <v>153827.94</v>
+      </c>
+      <c r="D3540" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942201</t>
+        </is>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" t="inlineStr">
+        <is>
+          <t>994810</t>
+        </is>
+      </c>
+      <c r="B3541" t="inlineStr">
+        <is>
+          <t>Regulador pres.cond.SANHUA LTF16H01-5/8S</t>
+        </is>
+      </c>
+      <c r="C3541" t="n">
+        <v>87282.7</v>
+      </c>
+      <c r="D3541" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994810</t>
+        </is>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" t="inlineStr">
+        <is>
+          <t>893964</t>
+        </is>
+      </c>
+      <c r="B3542" t="inlineStr">
+        <is>
+          <t>Vaso Expansión ATROM 7Lt. 0020118975</t>
+        </is>
+      </c>
+      <c r="C3542" t="n">
+        <v>118057.4</v>
+      </c>
+      <c r="D3542" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893964</t>
+        </is>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" t="inlineStr">
+        <is>
+          <t>920810</t>
+        </is>
+      </c>
+      <c r="B3543" t="inlineStr">
+        <is>
+          <t>Garrafa descartable MAP PRO -400gr------</t>
+        </is>
+      </c>
+      <c r="C3543" t="n">
+        <v>7298.95</v>
+      </c>
+      <c r="D3543" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/920810</t>
+        </is>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" t="inlineStr">
+        <is>
+          <t>938301</t>
+        </is>
+      </c>
+      <c r="B3544" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 65kW 380 TC-SS65</t>
+        </is>
+      </c>
+      <c r="C3544" t="n">
+        <v>11032189.8</v>
+      </c>
+      <c r="D3544" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938301</t>
+        </is>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" t="inlineStr">
+        <is>
+          <t>910616</t>
+        </is>
+      </c>
+      <c r="B3545" t="inlineStr">
+        <is>
+          <t>Tapa Metal Superior-121R00010PDG GSX1306</t>
+        </is>
+      </c>
+      <c r="C3545" t="n">
+        <v>153984.3</v>
+      </c>
+      <c r="D3545" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910616</t>
+        </is>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" t="inlineStr">
+        <is>
+          <t>908900</t>
+        </is>
+      </c>
+      <c r="B3546" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-20B (2 modulos)</t>
+        </is>
+      </c>
+      <c r="C3546" t="n">
+        <v>491301.05</v>
+      </c>
+      <c r="D3546" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" t="inlineStr">
+        <is>
+          <t>990002</t>
+        </is>
+      </c>
+      <c r="B3547" t="inlineStr">
+        <is>
+          <t>Tanque p/agua ST-200L s/calentador elec</t>
+        </is>
+      </c>
+      <c r="C3547" t="n">
+        <v>1323159.75</v>
+      </c>
+      <c r="D3547" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" t="inlineStr">
+        <is>
+          <t>942917</t>
+        </is>
+      </c>
+      <c r="B3548" t="inlineStr">
+        <is>
+          <t>PCB Evap.+Display SEP010-000116(BS11IN--</t>
+        </is>
+      </c>
+      <c r="C3548" t="n">
+        <v>279783.85</v>
+      </c>
+      <c r="D3548" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942917</t>
+        </is>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" t="inlineStr">
+        <is>
+          <t>917882</t>
+        </is>
+      </c>
+      <c r="B3549" t="inlineStr">
+        <is>
+          <t>Filt.Aire Izq.320x290p/9/12-201132590113</t>
+        </is>
+      </c>
+      <c r="C3549" t="n">
+        <v>5290.7</v>
+      </c>
+      <c r="D3549" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917882</t>
+        </is>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" t="inlineStr">
+        <is>
+          <t>999515</t>
+        </is>
+      </c>
+      <c r="B3550" t="inlineStr">
+        <is>
+          <t>CLIMATIZADOR TRSJ-140 GOLPExCAIDA 100011</t>
+        </is>
+      </c>
+      <c r="C3550" t="n">
+        <v>420679.9</v>
+      </c>
+      <c r="D3550" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999515</t>
+        </is>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" t="inlineStr">
+        <is>
+          <t>917545</t>
+        </is>
+      </c>
+      <c r="B3551" t="inlineStr">
+        <is>
+          <t>Motor Cnd.26WC -YDK24-6T- 2024004A0092--</t>
+        </is>
+      </c>
+      <c r="C3551" t="n">
+        <v>114110.15</v>
+      </c>
+      <c r="D3551" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917545</t>
+        </is>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" t="inlineStr">
+        <is>
+          <t>782114</t>
+        </is>
+      </c>
+      <c r="B3552" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x2.5mm---------</t>
+        </is>
+      </c>
+      <c r="C3552" t="n">
+        <v>178752</v>
+      </c>
+      <c r="D3552" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782114</t>
+        </is>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" t="inlineStr">
+        <is>
+          <t>115070</t>
+        </is>
+      </c>
+      <c r="B3553" t="inlineStr">
+        <is>
+          <t>Manom.BEYCA MM234/0a40kg-600lb/63mm/inf-</t>
+        </is>
+      </c>
+      <c r="C3553" t="n">
+        <v>7290.55</v>
+      </c>
+      <c r="D3553" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115070</t>
+        </is>
+      </c>
+    </row>
+    <row r="3554">
+      <c r="A3554" t="inlineStr">
+        <is>
+          <t>946258</t>
+        </is>
+      </c>
+      <c r="B3554" t="inlineStr">
+        <is>
+          <t>Termost.dig.progr.BlueStar HVAC10-------</t>
+        </is>
+      </c>
+      <c r="C3554" t="n">
+        <v>34680.4</v>
+      </c>
+      <c r="D3554" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946258</t>
+        </is>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" t="inlineStr">
+        <is>
+          <t>937207</t>
+        </is>
+      </c>
+      <c r="B3555" t="inlineStr">
+        <is>
+          <t>Motor LG EAU57945702--------------------</t>
+        </is>
+      </c>
+      <c r="C3555" t="n">
+        <v>121076.7</v>
+      </c>
+      <c r="D3555" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937207</t>
+        </is>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" t="inlineStr">
+        <is>
+          <t>937110</t>
+        </is>
+      </c>
+      <c r="B3556" t="inlineStr">
+        <is>
+          <t>PCB Ppal.ThermaV EBR79735906 (HN1639NK3)</t>
+        </is>
+      </c>
+      <c r="C3556" t="n">
+        <v>217168</v>
+      </c>
+      <c r="D3556" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937110</t>
+        </is>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" t="inlineStr">
+        <is>
+          <t>942202</t>
+        </is>
+      </c>
+      <c r="B3557" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-3350W ELITE 5  R32--</t>
+        </is>
+      </c>
+      <c r="C3557" t="n">
+        <v>369517.82</v>
+      </c>
+      <c r="D3557" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" t="inlineStr">
+        <is>
+          <t>893965</t>
+        </is>
+      </c>
+      <c r="B3558" t="inlineStr">
+        <is>
+          <t>PCB Ppal. ATROM  0020211395</t>
+        </is>
+      </c>
+      <c r="C3558" t="n">
+        <v>167321.85</v>
+      </c>
+      <c r="D3558" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893965</t>
+        </is>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" t="inlineStr">
+        <is>
+          <t>938302</t>
+        </is>
+      </c>
+      <c r="B3559" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 80kW 380 TC-SS80</t>
+        </is>
+      </c>
+      <c r="C3559" t="n">
+        <v>16852098.3</v>
+      </c>
+      <c r="D3559" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938302</t>
+        </is>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" t="inlineStr">
+        <is>
+          <t>910619</t>
+        </is>
+      </c>
+      <c r="B3560" t="inlineStr">
+        <is>
+          <t>Soporte Lateral ciego-0121R00354PDG</t>
+        </is>
+      </c>
+      <c r="C3560" t="n">
+        <v>166823.25</v>
+      </c>
+      <c r="D3560" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910619</t>
+        </is>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" t="inlineStr">
+        <is>
+          <t>908907</t>
+        </is>
+      </c>
+      <c r="B3561" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-30A (3 Modulos)</t>
+        </is>
+      </c>
+      <c r="C3561" t="n">
+        <v>441371.8</v>
+      </c>
+      <c r="D3561" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908907</t>
+        </is>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" t="inlineStr">
+        <is>
+          <t>900811</t>
+        </is>
+      </c>
+      <c r="B3562" t="inlineStr">
+        <is>
+          <t>Main Board TK-H3.3NH 30221000026</t>
+        </is>
+      </c>
+      <c r="C3562" t="n">
+        <v>350349.6</v>
+      </c>
+      <c r="D3562" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/900811</t>
+        </is>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" t="inlineStr">
+        <is>
+          <t>942919</t>
+        </is>
+      </c>
+      <c r="B3563" t="inlineStr">
+        <is>
+          <t>PCB Cond+borne SEP010-000117(BS11INV)---</t>
+        </is>
+      </c>
+      <c r="C3563" t="n">
+        <v>286542.65</v>
+      </c>
+      <c r="D3563" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942919</t>
+        </is>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" t="inlineStr">
+        <is>
+          <t>917700</t>
+        </is>
+      </c>
+      <c r="B3564" t="inlineStr">
+        <is>
+          <t>Filtro Aire 270X270 p/09--201132390523--</t>
+        </is>
+      </c>
+      <c r="C3564" t="n">
+        <v>4528.95</v>
+      </c>
+      <c r="D3564" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" t="inlineStr">
+        <is>
+          <t>942923</t>
+        </is>
+      </c>
+      <c r="B3565" t="inlineStr">
+        <is>
+          <t>Motor 21w. Evp. 22001-000297_CT(BS11INV)</t>
+        </is>
+      </c>
+      <c r="C3565" t="n">
+        <v>93501.35000000001</v>
+      </c>
+      <c r="D3565" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942923</t>
+        </is>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" t="inlineStr">
+        <is>
+          <t>942933</t>
+        </is>
+      </c>
+      <c r="B3566" t="inlineStr">
+        <is>
+          <t>Bobina 220v. 92001-000015_CT(BS11INV)---</t>
+        </is>
+      </c>
+      <c r="C3566" t="n">
+        <v>26024.15</v>
+      </c>
+      <c r="D3566" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942933</t>
+        </is>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" t="inlineStr">
+        <is>
+          <t>116202</t>
+        </is>
+      </c>
+      <c r="B3567" t="inlineStr">
+        <is>
+          <t>Filtro cobre 5gr.BlueStar-s/chicote SD2-</t>
+        </is>
+      </c>
+      <c r="C3567" t="n">
+        <v>1149.55</v>
+      </c>
+      <c r="D3567" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/116202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" t="inlineStr">
+        <is>
+          <t>917549</t>
+        </is>
+      </c>
+      <c r="B3568" t="inlineStr">
+        <is>
+          <t>Motor Cnd.35WC -YDK36-6-  202400400723--</t>
+        </is>
+      </c>
+      <c r="C3568" t="n">
+        <v>144455.5</v>
+      </c>
+      <c r="D3568" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917549</t>
+        </is>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" t="inlineStr">
+        <is>
+          <t>115074</t>
+        </is>
+      </c>
+      <c r="B3569" t="inlineStr">
+        <is>
+          <t>Vacuom.BEYCA VM234/30"-0-63mm/inf-------</t>
+        </is>
+      </c>
+      <c r="C3569" t="n">
+        <v>8417.34</v>
+      </c>
+      <c r="D3569" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115074</t>
+        </is>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" t="inlineStr">
+        <is>
+          <t>998116</t>
+        </is>
+      </c>
+      <c r="B3570" t="inlineStr">
+        <is>
+          <t>Motocomp.--OFERTA--GMCC2275FR R410------</t>
+        </is>
+      </c>
+      <c r="C3570" t="n">
+        <v>91077.60000000001</v>
+      </c>
+      <c r="D3570" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/998116</t>
+        </is>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" t="inlineStr">
+        <is>
+          <t>979504</t>
+        </is>
+      </c>
+      <c r="B3571" t="inlineStr">
+        <is>
+          <t>U.C. M3OG-21HFN8-Q 21000BTU R32 index:30</t>
+        </is>
+      </c>
+      <c r="C3571" t="n">
+        <v>1214409.55</v>
+      </c>
+      <c r="D3571" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979504</t>
+        </is>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" t="inlineStr">
+        <is>
+          <t>942913</t>
+        </is>
+      </c>
+      <c r="B3572" t="inlineStr">
+        <is>
+          <t>Serpentina Evp.92011-012913(BS11INV)09H-</t>
+        </is>
+      </c>
+      <c r="C3572" t="n">
+        <v>278828.2</v>
+      </c>
+      <c r="D3572" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942913</t>
+        </is>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" t="inlineStr">
+        <is>
+          <t>999910</t>
+        </is>
+      </c>
+      <c r="B3573" t="inlineStr">
+        <is>
+          <t>TOE30U-55HDN1 Cond.5Tr. 500005 S/PCB----</t>
+        </is>
+      </c>
+      <c r="C3573" t="n">
+        <v>439294.3</v>
+      </c>
+      <c r="D3573" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999910</t>
+        </is>
+      </c>
+    </row>
+    <row r="3574">
+      <c r="A3574" t="inlineStr">
+        <is>
+          <t>994596</t>
+        </is>
+      </c>
+      <c r="B3574" t="inlineStr">
+        <is>
+          <t>Valv.Reg.Pres.evap.SANHUA CTF16H51.-5/8-</t>
+        </is>
+      </c>
+      <c r="C3574" t="n">
+        <v>91576.2</v>
+      </c>
+      <c r="D3574" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994596</t>
+        </is>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" t="inlineStr">
+        <is>
+          <t>946257</t>
+        </is>
+      </c>
+      <c r="B3575" t="inlineStr">
+        <is>
+          <t>Termost.dig.progr.BlueStar HVAC10-WIFI--</t>
+        </is>
+      </c>
+      <c r="C3575" t="n">
+        <v>45026.35</v>
+      </c>
+      <c r="D3575" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946257</t>
+        </is>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" t="inlineStr">
+        <is>
+          <t>942804</t>
+        </is>
+      </c>
+      <c r="B3576" t="inlineStr">
+        <is>
+          <t>PCB Ctrol. 810900560B (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3576" t="n">
+        <v>68446.7</v>
+      </c>
+      <c r="D3576" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942804</t>
+        </is>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" t="inlineStr">
+        <is>
+          <t>853004</t>
+        </is>
+      </c>
+      <c r="B3577" t="inlineStr">
+        <is>
+          <t>PCB Display SEP001-000017 (TA8-32)</t>
+        </is>
+      </c>
+      <c r="C3577" t="n">
+        <v>35428.3</v>
+      </c>
+      <c r="D3577" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/853004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3578">
+      <c r="A3578" t="inlineStr">
+        <is>
+          <t>937206</t>
+        </is>
+      </c>
+      <c r="B3578" t="inlineStr">
+        <is>
+          <t>Motor LG EAU57945712--------------------</t>
+        </is>
+      </c>
+      <c r="C3578" t="n">
+        <v>121076.7</v>
+      </c>
+      <c r="D3578" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937206</t>
+        </is>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" t="inlineStr">
+        <is>
+          <t>937173</t>
+        </is>
+      </c>
+      <c r="B3579" t="inlineStr">
+        <is>
+          <t>PCB Assembly EBR77627617 (ARUN060LSS0)</t>
+        </is>
+      </c>
+      <c r="C3579" t="n">
+        <v>146075.95</v>
+      </c>
+      <c r="D3579" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937173</t>
+        </is>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" t="inlineStr">
+        <is>
+          <t>994802</t>
+        </is>
+      </c>
+      <c r="B3580" t="inlineStr">
+        <is>
+          <t>Regulador pres.succ.SANHUA XTF22H01-7/8S</t>
+        </is>
+      </c>
+      <c r="C3580" t="n">
+        <v>81590.35000000001</v>
+      </c>
+      <c r="D3580" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994802</t>
+        </is>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" t="inlineStr">
+        <is>
+          <t>942203</t>
+        </is>
+      </c>
+      <c r="B3581" t="inlineStr">
+        <is>
+          <t>UE."TCL" ONOFF TACA-3350W ELITE 5  R32--</t>
+        </is>
+      </c>
+      <c r="C3581" t="n">
+        <v>158364.78</v>
+      </c>
+      <c r="D3581" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942203</t>
+        </is>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" t="inlineStr">
+        <is>
+          <t>994811</t>
+        </is>
+      </c>
+      <c r="B3582" t="inlineStr">
+        <is>
+          <t>Regulador pres.cond.SANHUA LTF22H01-7/8S</t>
+        </is>
+      </c>
+      <c r="C3582" t="n">
+        <v>88958.55</v>
+      </c>
+      <c r="D3582" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994811</t>
+        </is>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" t="inlineStr">
+        <is>
+          <t>893966</t>
+        </is>
+      </c>
+      <c r="B3583" t="inlineStr">
+        <is>
+          <t>Transf. Ignitor chispa ATROM D003202244</t>
+        </is>
+      </c>
+      <c r="C3583" t="n">
+        <v>15096.5</v>
+      </c>
+      <c r="D3583" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893966</t>
+        </is>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" t="inlineStr">
+        <is>
+          <t>938303</t>
+        </is>
+      </c>
+      <c r="B3584" t="inlineStr">
+        <is>
+          <t>Bomba calor ONOFF Scrol 130kW 380 TCS130</t>
+        </is>
+      </c>
+      <c r="C3584" t="n">
+        <v>18962090.4</v>
+      </c>
+      <c r="D3584" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938303</t>
+        </is>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" t="inlineStr">
+        <is>
+          <t>910620</t>
+        </is>
+      </c>
+      <c r="B3585" t="inlineStr">
+        <is>
+          <t>Rejilla Lateral 0121R00346PDGLS GSX13060</t>
+        </is>
+      </c>
+      <c r="C3585" t="n">
+        <v>348590.65</v>
+      </c>
+      <c r="D3585" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910620</t>
+        </is>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" t="inlineStr">
+        <is>
+          <t>908908</t>
+        </is>
+      </c>
+      <c r="B3586" t="inlineStr">
+        <is>
+          <t>Y-Branch ODUs HZG-30B (3 modulos)</t>
+        </is>
+      </c>
+      <c r="C3586" t="n">
+        <v>635105.6</v>
+      </c>
+      <c r="D3586" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908908</t>
+        </is>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="inlineStr">
+        <is>
+          <t>990004</t>
+        </is>
+      </c>
+      <c r="B3587" t="inlineStr">
+        <is>
+          <t>Tanque p/agua ST-300L s/calentador elec</t>
+        </is>
+      </c>
+      <c r="C3587" t="n">
+        <v>1761927.75</v>
+      </c>
+      <c r="D3587" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="inlineStr">
+        <is>
+          <t>917883</t>
+        </is>
+      </c>
+      <c r="B3588" t="inlineStr">
+        <is>
+          <t>Filtro Aire 380x350 p/18----201132790091</t>
+        </is>
+      </c>
+      <c r="C3588" t="n">
+        <v>9708.85</v>
+      </c>
+      <c r="D3588" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917883</t>
+        </is>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" t="inlineStr">
+        <is>
+          <t>906102</t>
+        </is>
+      </c>
+      <c r="B3589" t="inlineStr">
+        <is>
+          <t>Bomba Vacio"BlueStar"VP215 51 L/min--2et</t>
+        </is>
+      </c>
+      <c r="C3589" t="n">
+        <v>153596.5</v>
+      </c>
+      <c r="D3589" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906102</t>
+        </is>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" t="inlineStr">
+        <is>
+          <t>906509</t>
+        </is>
+      </c>
+      <c r="B3590" t="inlineStr">
+        <is>
+          <t>Motoc."BlueStar"1/8 -ADW43 -R134-110W---</t>
+        </is>
+      </c>
+      <c r="C3590" t="n">
+        <v>50455.55</v>
+      </c>
+      <c r="D3590" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906509</t>
+        </is>
+      </c>
+    </row>
+    <row r="3591">
+      <c r="A3591" t="inlineStr">
+        <is>
+          <t>942943</t>
+        </is>
+      </c>
+      <c r="B3591" t="inlineStr">
+        <is>
+          <t>Compresor 92014-000818 (BS11INV) 12H----</t>
+        </is>
+      </c>
+      <c r="C3591" t="n">
+        <v>381484.4</v>
+      </c>
+      <c r="D3591" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942943</t>
+        </is>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" t="inlineStr">
+        <is>
+          <t>942925</t>
+        </is>
+      </c>
+      <c r="B3592" t="inlineStr">
+        <is>
+          <t>Motor Step 12v. 22001-000313_CT(BS11INV)</t>
+        </is>
+      </c>
+      <c r="C3592" t="n">
+        <v>17838.8</v>
+      </c>
+      <c r="D3592" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942925</t>
+        </is>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" t="inlineStr">
+        <is>
+          <t>942935</t>
+        </is>
+      </c>
+      <c r="B3593" t="inlineStr">
+        <is>
+          <t>Valv.Inver. s/Bob.SEC006-000034(BS11INV)</t>
+        </is>
+      </c>
+      <c r="C3593" t="n">
+        <v>76881.35000000001</v>
+      </c>
+      <c r="D3593" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942935</t>
+        </is>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" t="inlineStr">
+        <is>
+          <t>255345</t>
+        </is>
+      </c>
+      <c r="B3594" t="inlineStr">
+        <is>
+          <t>EXHIBIDORA VERTICAL PHILCO 229L PHEV230B</t>
+        </is>
+      </c>
+      <c r="C3594" t="n">
+        <v>617267</v>
+      </c>
+      <c r="D3594" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255345</t>
+        </is>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" t="inlineStr">
+        <is>
+          <t>116200</t>
+        </is>
+      </c>
+      <c r="B3595" t="inlineStr">
+        <is>
+          <t>Filtro cobr.10gr.BlueStar-s/chicote SD2-</t>
+        </is>
+      </c>
+      <c r="C3595" t="n">
+        <v>1412.7</v>
+      </c>
+      <c r="D3595" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/116200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" t="inlineStr">
+        <is>
+          <t>999012</t>
+        </is>
+      </c>
+      <c r="B3596" t="inlineStr">
+        <is>
+          <t>U.C.TADIRAN MULTI 1:4A DISTRIB.TAPA 4360</t>
+        </is>
+      </c>
+      <c r="C3596" t="n">
+        <v>440236.1</v>
+      </c>
+      <c r="D3596" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999012</t>
+        </is>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" t="inlineStr">
+        <is>
+          <t>917548</t>
+        </is>
+      </c>
+      <c r="B3597" t="inlineStr">
+        <is>
+          <t>Motor Cnd.53WC -YDK48-6H- 202400410505--</t>
+        </is>
+      </c>
+      <c r="C3597" t="n">
+        <v>146422.2</v>
+      </c>
+      <c r="D3597" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917548</t>
+        </is>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" t="inlineStr">
+        <is>
+          <t>994482</t>
+        </is>
+      </c>
+      <c r="B3598" t="inlineStr">
+        <is>
+          <t>Valvula Elect.SANHUA LPF10-002----------</t>
+        </is>
+      </c>
+      <c r="C3598" t="n">
+        <v>59042.55</v>
+      </c>
+      <c r="D3598" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994482</t>
+        </is>
+      </c>
+    </row>
+    <row r="3599">
+      <c r="A3599" t="inlineStr">
+        <is>
+          <t>782020</t>
+        </is>
+      </c>
+      <c r="B3599" t="inlineStr">
+        <is>
+          <t>Mt.cable taller IRAM-2x1mm--------------</t>
+        </is>
+      </c>
+      <c r="C3599" t="n">
+        <v>851.73</v>
+      </c>
+      <c r="D3599" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782020</t>
+        </is>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" t="inlineStr">
+        <is>
+          <t>906120</t>
+        </is>
+      </c>
+      <c r="B3600" t="inlineStr">
+        <is>
+          <t>Tapon de aceite para bomba BlueStar-----</t>
+        </is>
+      </c>
+      <c r="C3600" t="n">
+        <v>1911.3</v>
+      </c>
+      <c r="D3600" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906120</t>
+        </is>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>914050</t>
+        </is>
+      </c>
+      <c r="B3601" t="inlineStr">
+        <is>
+          <t>U.C."TADIRAN" TA8-5000FC 5200w R410 "A"-</t>
+        </is>
+      </c>
+      <c r="C3601" t="n">
+        <v>189520.13</v>
+      </c>
+      <c r="D3601" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/914050</t>
+        </is>
+      </c>
+    </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>979202</t>
+        </is>
+      </c>
+      <c r="B3602" t="inlineStr">
+        <is>
+          <t>U.C. ATOM TA-V28WDHN1(AtB)  8kW---------</t>
+        </is>
+      </c>
+      <c r="C3602" t="n">
+        <v>1229963.1</v>
+      </c>
+      <c r="D3602" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>942915</t>
+        </is>
+      </c>
+      <c r="B3603" t="inlineStr">
+        <is>
+          <t>Serpentina Evp.92011-012266(BS11INV)12H</t>
+        </is>
+      </c>
+      <c r="C3603" t="n">
+        <v>278828.2</v>
+      </c>
+      <c r="D3603" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942915</t>
+        </is>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>999152</t>
+        </is>
+      </c>
+      <c r="B3604" t="inlineStr">
+        <is>
+          <t>TTI-55HWDN1 Evp. 5Tr. FC  60060 Detalles</t>
+        </is>
+      </c>
+      <c r="C3604" t="n">
+        <v>463504.1</v>
+      </c>
+      <c r="D3604" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999152</t>
+        </is>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>946256</t>
+        </is>
+      </c>
+      <c r="B3605" t="inlineStr">
+        <is>
+          <t>Termost.dig.progr.BlueStar HVAC11-------</t>
+        </is>
+      </c>
+      <c r="C3605" t="n">
+        <v>26550.45</v>
+      </c>
+      <c r="D3605" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946256</t>
+        </is>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>590095</t>
+        </is>
+      </c>
+      <c r="B3606" t="inlineStr">
+        <is>
+          <t>Filtro WHITE"ECO"35-1/4x5/16 sol.molecu-</t>
+        </is>
+      </c>
+      <c r="C3606" t="n">
+        <v>9995.49</v>
+      </c>
+      <c r="D3606" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/590095</t>
+        </is>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>937225</t>
+        </is>
+      </c>
+      <c r="B3607" t="inlineStr">
+        <is>
+          <t>Motor ARNU07/15 EAU62004011-------------</t>
+        </is>
+      </c>
+      <c r="C3607" t="n">
+        <v>85689.95</v>
+      </c>
+      <c r="D3607" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937225</t>
+        </is>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>937124</t>
+        </is>
+      </c>
+      <c r="B3608" t="inlineStr">
+        <is>
+          <t>Filter,AC Line EAM62452301/EBR81969701</t>
+        </is>
+      </c>
+      <c r="C3608" t="n">
+        <v>101409.7</v>
+      </c>
+      <c r="D3608" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>937224</t>
+        </is>
+      </c>
+      <c r="B3609" t="inlineStr">
+        <is>
+          <t>Bomba Cond. AHA76461701 ARNU07/24G4M1A4-</t>
+        </is>
+      </c>
+      <c r="C3609" t="n">
+        <v>44403.1</v>
+      </c>
+      <c r="D3609" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937224</t>
+        </is>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>913675</t>
+        </is>
+      </c>
+      <c r="B3610" t="inlineStr">
+        <is>
+          <t>Sellador fuga EXTERNAL P-p/plasTR1172.01</t>
+        </is>
+      </c>
+      <c r="C3610" t="n">
+        <v>11703.25</v>
+      </c>
+      <c r="D3610" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913675</t>
+        </is>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>917001</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr">
+        <is>
+          <t>Capacitor  1 MFx450V-"BlueStar"-CBB60-3-</t>
+        </is>
+      </c>
+      <c r="C3611" t="n">
+        <v>1024.9</v>
+      </c>
+      <c r="D3611" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>906008</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr">
+        <is>
+          <t>Pinza Amperometrica BlueStar TA8315C----</t>
+        </is>
+      </c>
+      <c r="C3612" t="n">
+        <v>30206.85</v>
+      </c>
+      <c r="D3612" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>295510</t>
+        </is>
+      </c>
+      <c r="B3613" t="inlineStr">
+        <is>
+          <t>Kit Sal.Gas N.F.Delfis.d10/6--0KITCONC00</t>
+        </is>
+      </c>
+      <c r="C3613" t="n">
+        <v>26176.5</v>
+      </c>
+      <c r="D3613" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/295510</t>
+        </is>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>942204</t>
+        </is>
+      </c>
+      <c r="B3614" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-5400W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3614" t="n">
+        <v>540467.0600000001</v>
+      </c>
+      <c r="D3614" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942204</t>
+        </is>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>893968</t>
+        </is>
+      </c>
+      <c r="B3615" t="inlineStr">
+        <is>
+          <t>Diafragma Fan ATROM H28 D003202523</t>
+        </is>
+      </c>
+      <c r="C3615" t="n">
+        <v>1731.25</v>
+      </c>
+      <c r="D3615" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893968</t>
+        </is>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>919110</t>
+        </is>
+      </c>
+      <c r="B3616" t="inlineStr">
+        <is>
+          <t>Garrafa descart.BERNZ-MAPP-MDC-1316*C---</t>
+        </is>
+      </c>
+      <c r="C3616" t="n">
+        <v>10595.25</v>
+      </c>
+      <c r="D3616" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/919110</t>
+        </is>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>253005</t>
+        </is>
+      </c>
+      <c r="B3617" t="inlineStr">
+        <is>
+          <t>Mini.Sol"BlueStar"1/4m-oxi/but---certif-</t>
+        </is>
+      </c>
+      <c r="C3617" t="n">
+        <v>612197.7</v>
+      </c>
+      <c r="D3617" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/253005</t>
+        </is>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>910625</t>
+        </is>
+      </c>
+      <c r="B3618" t="inlineStr">
+        <is>
+          <t>Rejilla Lateral 0121R00346PDGRS GSX13060</t>
+        </is>
+      </c>
+      <c r="C3618" t="n">
+        <v>348590.65</v>
+      </c>
+      <c r="D3618" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910625</t>
+        </is>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>185515</t>
+        </is>
+      </c>
+      <c r="B3619" t="inlineStr">
+        <is>
+          <t>Tubo 56,7Kg-FREON 134a-CHEMOURS-Retornab</t>
+        </is>
+      </c>
+      <c r="C3619" t="n">
+        <v>1079552.1</v>
+      </c>
+      <c r="D3619" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/185515</t>
+        </is>
+      </c>
+    </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>836010</t>
+        </is>
+      </c>
+      <c r="B3620" t="inlineStr">
+        <is>
+          <t>Plaqueta universal NO FROST BASIC-1vent-</t>
+        </is>
+      </c>
+      <c r="C3620" t="n">
+        <v>31481.05</v>
+      </c>
+      <c r="D3620" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/836010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>908906</t>
+        </is>
+      </c>
+      <c r="B3621" t="inlineStr">
+        <is>
+          <t>Y-Branch IDUs FQG-B335A menor a 33,56 kW</t>
+        </is>
+      </c>
+      <c r="C3621" t="n">
+        <v>71895.35000000001</v>
+      </c>
+      <c r="D3621" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908906</t>
+        </is>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>900810</t>
+        </is>
+      </c>
+      <c r="B3622" t="inlineStr">
+        <is>
+          <t>Main Board TK-H5.5NH 300027060479</t>
+        </is>
+      </c>
+      <c r="C3622" t="n">
+        <v>305586.4</v>
+      </c>
+      <c r="D3622" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/900810</t>
+        </is>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>917884</t>
+        </is>
+      </c>
+      <c r="B3623" t="inlineStr">
+        <is>
+          <t>Filtro Aire 400x350 p/24----201133090127</t>
+        </is>
+      </c>
+      <c r="C3623" t="n">
+        <v>8365.4</v>
+      </c>
+      <c r="D3623" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917884</t>
+        </is>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>942937</t>
+        </is>
+      </c>
+      <c r="B3624" t="inlineStr">
+        <is>
+          <t>Tornillo p/Bob.92008-0002451_CT(BS11INV)</t>
+        </is>
+      </c>
+      <c r="C3624" t="n">
+        <v>1689.7</v>
+      </c>
+      <c r="D3624" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942937</t>
+        </is>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>917518</t>
+        </is>
+      </c>
+      <c r="B3625" t="inlineStr">
+        <is>
+          <t>Motor Cnd.63WC (YDK24-6B) 202400400491--</t>
+        </is>
+      </c>
+      <c r="C3625" t="n">
+        <v>107905.35</v>
+      </c>
+      <c r="D3625" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917518</t>
+        </is>
+      </c>
+    </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>906121</t>
+        </is>
+      </c>
+      <c r="B3626" t="inlineStr">
+        <is>
+          <t>Tapa de valvula para bomba BlueStar-1/4-</t>
+        </is>
+      </c>
+      <c r="C3626" t="n">
+        <v>623.25</v>
+      </c>
+      <c r="D3626" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906121</t>
+        </is>
+      </c>
+    </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>115062</t>
+        </is>
+      </c>
+      <c r="B3627" t="inlineStr">
+        <is>
+          <t>Manom.BEYCA MM234/0a10Kg-150lb/63mm/inf-</t>
+        </is>
+      </c>
+      <c r="C3627" t="n">
+        <v>6973.94</v>
+      </c>
+      <c r="D3627" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/115062</t>
+        </is>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>998100</t>
+        </is>
+      </c>
+      <c r="B3628" t="inlineStr">
+        <is>
+          <t>Motocomp.--OFERTA--EMYE70CLP------------</t>
+        </is>
+      </c>
+      <c r="C3628" t="n">
+        <v>62948.25</v>
+      </c>
+      <c r="D3628" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/998100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>979506</t>
+        </is>
+      </c>
+      <c r="B3629" t="inlineStr">
+        <is>
+          <t>U.C. M3OA-27HFN8-Q 27000BTU R32 index:36</t>
+        </is>
+      </c>
+      <c r="C3629" t="n">
+        <v>1337813.05</v>
+      </c>
+      <c r="D3629" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979506</t>
+        </is>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>942945</t>
+        </is>
+      </c>
+      <c r="B3630" t="inlineStr">
+        <is>
+          <t>Serpentina Cond.92011-012268(BS11INV)---</t>
+        </is>
+      </c>
+      <c r="C3630" t="n">
+        <v>376913.9</v>
+      </c>
+      <c r="D3630" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942945</t>
+        </is>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>999136</t>
+        </is>
+      </c>
+      <c r="B3631" t="inlineStr">
+        <is>
+          <t>TOE30U-55HD Cond.Inver S:50009 Tapon----</t>
+        </is>
+      </c>
+      <c r="C3631" t="n">
+        <v>934501.05</v>
+      </c>
+      <c r="D3631" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999136</t>
+        </is>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>946259</t>
+        </is>
+      </c>
+      <c r="B3632" t="inlineStr">
+        <is>
+          <t>Termost.dig.progr.BlueStar QD-HVAC21----</t>
+        </is>
+      </c>
+      <c r="C3632" t="n">
+        <v>39541.75</v>
+      </c>
+      <c r="D3632" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946259</t>
+        </is>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>942806</t>
+        </is>
+      </c>
+      <c r="B3633" t="inlineStr">
+        <is>
+          <t>Modulo WIFI 810900458H (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3633" t="n">
+        <v>21301.3</v>
+      </c>
+      <c r="D3633" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942806</t>
+        </is>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>937174</t>
+        </is>
+      </c>
+      <c r="B3634" t="inlineStr">
+        <is>
+          <t>PCB Assembly EBR79004823</t>
+        </is>
+      </c>
+      <c r="C3634" t="n">
+        <v>62352.7</v>
+      </c>
+      <c r="D3634" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937174</t>
+        </is>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>994803</t>
+        </is>
+      </c>
+      <c r="B3635" t="inlineStr">
+        <is>
+          <t>Regulador pres.succ.SANHUA XTF28H01-11/8</t>
+        </is>
+      </c>
+      <c r="C3635" t="n">
+        <v>118943.8</v>
+      </c>
+      <c r="D3635" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994803</t>
+        </is>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>295560</t>
+        </is>
+      </c>
+      <c r="B3636" t="inlineStr">
+        <is>
+          <t>Kit Sal.Gas Fond.Cond.d60/100-0CONDASP00</t>
+        </is>
+      </c>
+      <c r="C3636" t="n">
+        <v>98348.85000000001</v>
+      </c>
+      <c r="D3636" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/295560</t>
+        </is>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>942205</t>
+        </is>
+      </c>
+      <c r="B3637" t="inlineStr">
+        <is>
+          <t>UE."TCL" ONOFF TACA-5400W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3637" t="n">
+        <v>231628.74</v>
+      </c>
+      <c r="D3637" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942205</t>
+        </is>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>979956</t>
+        </is>
+      </c>
+      <c r="B3638" t="inlineStr">
+        <is>
+          <t>Termost. p/enfriadoras TADIRAN KJRM-120D</t>
+        </is>
+      </c>
+      <c r="C3638" t="n">
+        <v>217320.35</v>
+      </c>
+      <c r="D3638" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979956</t>
+        </is>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>910628</t>
+        </is>
+      </c>
+      <c r="B3639" t="inlineStr">
+        <is>
+          <t>Base Panel Metal 0121R00006PDG GSX130605</t>
+        </is>
+      </c>
+      <c r="C3639" t="n">
+        <v>215727.6</v>
+      </c>
+      <c r="D3639" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910628</t>
+        </is>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>908905</t>
+        </is>
+      </c>
+      <c r="B3640" t="inlineStr">
+        <is>
+          <t>Y-Branch IDUs FQG-B506A 33,5 a 50,6 kW</t>
+        </is>
+      </c>
+      <c r="C3640" t="n">
+        <v>81881.2</v>
+      </c>
+      <c r="D3640" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908905</t>
+        </is>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>990006</t>
+        </is>
+      </c>
+      <c r="B3641" t="inlineStr">
+        <is>
+          <t>Buffer tanque agua BFS-100 s/calen elctr</t>
+        </is>
+      </c>
+      <c r="C3641" t="n">
+        <v>719853.75</v>
+      </c>
+      <c r="D3641" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990006</t>
+        </is>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>917946</t>
+        </is>
+      </c>
+      <c r="B3642" t="inlineStr">
+        <is>
+          <t>Filtro Aire 400X350 p/24--201133090126--</t>
+        </is>
+      </c>
+      <c r="C3642" t="n">
+        <v>8365.4</v>
+      </c>
+      <c r="D3642" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917946</t>
+        </is>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>942939</t>
+        </is>
+      </c>
+      <c r="B3643" t="inlineStr">
+        <is>
+          <t>Valv.Serv.1/4 SEC009-000003 (BS11INV)---</t>
+        </is>
+      </c>
+      <c r="C3643" t="n">
+        <v>7949.9</v>
+      </c>
+      <c r="D3643" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942939</t>
+        </is>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>917961</t>
+        </is>
+      </c>
+      <c r="B3644" t="inlineStr">
+        <is>
+          <t>Motor Evp.62WCN RPG45-11002012000503----</t>
+        </is>
+      </c>
+      <c r="C3644" t="n">
+        <v>100855.7</v>
+      </c>
+      <c r="D3644" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917961</t>
+        </is>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>906122</t>
+        </is>
+      </c>
+      <c r="B3645" t="inlineStr">
+        <is>
+          <t>Tapa de valvula para bomba BlueStar-3/8-</t>
+        </is>
+      </c>
+      <c r="C3645" t="n">
+        <v>761.75</v>
+      </c>
+      <c r="D3645" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906122</t>
+        </is>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>999134</t>
+        </is>
+      </c>
+      <c r="B3646" t="inlineStr">
+        <is>
+          <t>TUE55HRD Evap.Inver S:60052 Instalada---</t>
+        </is>
+      </c>
+      <c r="C3646" t="n">
+        <v>720920.2</v>
+      </c>
+      <c r="D3646" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999134</t>
+        </is>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>937125</t>
+        </is>
+      </c>
+      <c r="B3647" t="inlineStr">
+        <is>
+          <t>PCB Assembly EBR74363401 ARUN180LTE4</t>
+        </is>
+      </c>
+      <c r="C3647" t="n">
+        <v>139981.95</v>
+      </c>
+      <c r="D3647" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937125</t>
+        </is>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>942206</t>
+        </is>
+      </c>
+      <c r="B3648" t="inlineStr">
+        <is>
+          <t>UC."TCL" ONOFF TACA-6500W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3648" t="n">
+        <v>606318.16</v>
+      </c>
+      <c r="D3648" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942206</t>
+        </is>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>893970</t>
+        </is>
+      </c>
+      <c r="B3649" t="inlineStr">
+        <is>
+          <t>O*Ring (pk10) ATROM H24/28 D003202011</t>
+        </is>
+      </c>
+      <c r="C3649" t="n">
+        <v>1578.9</v>
+      </c>
+      <c r="D3649" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893970</t>
+        </is>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>979958</t>
+        </is>
+      </c>
+      <c r="B3650" t="inlineStr">
+        <is>
+          <t>Termost. p/enfriadoras TADIRAN KJR-120A</t>
+        </is>
+      </c>
+      <c r="C3650" t="n">
+        <v>234037.3</v>
+      </c>
+      <c r="D3650" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979958</t>
+        </is>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>910643</t>
+        </is>
+      </c>
+      <c r="B3651" t="inlineStr">
+        <is>
+          <t>Valv.servic. Líquido 3/8 -0151R00078----</t>
+        </is>
+      </c>
+      <c r="C3651" t="n">
+        <v>39694.1</v>
+      </c>
+      <c r="D3651" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910643</t>
+        </is>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>908901</t>
+        </is>
+      </c>
+      <c r="B3652" t="inlineStr">
+        <is>
+          <t>Y-Branch IDUs FQG-B730A 50,6 a 73 kW</t>
+        </is>
+      </c>
+      <c r="C3652" t="n">
+        <v>121824.6</v>
+      </c>
+      <c r="D3652" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908901</t>
+        </is>
+      </c>
+    </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>962618</t>
+        </is>
+      </c>
+      <c r="B3653" t="inlineStr">
+        <is>
+          <t>TermHig.BlueSt.Elite.DT2-14CF2DT(max/min</t>
+        </is>
+      </c>
+      <c r="C3653" t="n">
+        <v>16384.55</v>
+      </c>
+      <c r="D3653" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/962618</t>
+        </is>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>917537</t>
+        </is>
+      </c>
+      <c r="B3654" t="inlineStr">
+        <is>
+          <t>Trafo Cond.24H-220/10.5v--202300900179--</t>
+        </is>
+      </c>
+      <c r="C3654" t="n">
+        <v>26370.4</v>
+      </c>
+      <c r="D3654" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917537</t>
+        </is>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>942941</t>
+        </is>
+      </c>
+      <c r="B3655" t="inlineStr">
+        <is>
+          <t>Valv.Serv.3/8 SEC009-000004 (BS11INV)---</t>
+        </is>
+      </c>
+      <c r="C3655" t="n">
+        <v>14459.4</v>
+      </c>
+      <c r="D3655" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942941</t>
+        </is>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>116201</t>
+        </is>
+      </c>
+      <c r="B3656" t="inlineStr">
+        <is>
+          <t>Filtro cobr.15gr.BlueStar-s/chicote SD2-</t>
+        </is>
+      </c>
+      <c r="C3656" t="n">
+        <v>1620.45</v>
+      </c>
+      <c r="D3656" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/116201</t>
+        </is>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>917962</t>
+        </is>
+      </c>
+      <c r="B3657" t="inlineStr">
+        <is>
+          <t>Motor Cnd.35WCN YDK36-6-2024004A0094----</t>
+        </is>
+      </c>
+      <c r="C3657" t="n">
+        <v>78695.7</v>
+      </c>
+      <c r="D3657" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917962</t>
+        </is>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>979508</t>
+        </is>
+      </c>
+      <c r="B3658" t="inlineStr">
+        <is>
+          <t>U.C. M4OE-28HFN8-Q 28000BTU R32 index:48</t>
+        </is>
+      </c>
+      <c r="C3658" t="n">
+        <v>1567792.3</v>
+      </c>
+      <c r="D3658" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979508</t>
+        </is>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>942953</t>
+        </is>
+      </c>
+      <c r="B3659" t="inlineStr">
+        <is>
+          <t>Caño Ent.Evap.1/4F SEC001-000023(BS11IN-</t>
+        </is>
+      </c>
+      <c r="C3659" t="n">
+        <v>18074.25</v>
+      </c>
+      <c r="D3659" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942953</t>
+        </is>
+      </c>
+    </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>999137</t>
+        </is>
+      </c>
+      <c r="B3660" t="inlineStr">
+        <is>
+          <t>MUB36HR Evap.3Tr S:0007 Instalada-------</t>
+        </is>
+      </c>
+      <c r="C3660" t="n">
+        <v>351817.7</v>
+      </c>
+      <c r="D3660" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999137</t>
+        </is>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>942808</t>
+        </is>
+      </c>
+      <c r="B3661" t="inlineStr">
+        <is>
+          <t>Flotante Doble 810900660A (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3661" t="n">
+        <v>10955.35</v>
+      </c>
+      <c r="D3661" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942808</t>
+        </is>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>937126</t>
+        </is>
+      </c>
+      <c r="B3662" t="inlineStr">
+        <is>
+          <t>PCB Evap. LG ARNU09-24GVEA2 EBR39566203</t>
+        </is>
+      </c>
+      <c r="C3662" t="n">
+        <v>110135.2</v>
+      </c>
+      <c r="D3662" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937126</t>
+        </is>
+      </c>
+    </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>994804</t>
+        </is>
+      </c>
+      <c r="B3663" t="inlineStr">
+        <is>
+          <t>Regulador pres.succ.SANHUA XTF35H01-13/8</t>
+        </is>
+      </c>
+      <c r="C3663" t="n">
+        <v>119996.4</v>
+      </c>
+      <c r="D3663" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994804</t>
+        </is>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>942207</t>
+        </is>
+      </c>
+      <c r="B3664" t="inlineStr">
+        <is>
+          <t>UE."TCL" ONOFF TACA-6500W ELITE 4  R32--</t>
+        </is>
+      </c>
+      <c r="C3664" t="n">
+        <v>259850.64</v>
+      </c>
+      <c r="D3664" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942207</t>
+        </is>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>946108</t>
+        </is>
+      </c>
+      <c r="B3665" t="inlineStr">
+        <is>
+          <t>Pico p/sold BlueStar JH-3W--------------</t>
+        </is>
+      </c>
+      <c r="C3665" t="n">
+        <v>32686</v>
+      </c>
+      <c r="D3665" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946108</t>
+        </is>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>910649</t>
+        </is>
+      </c>
+      <c r="B3666" t="inlineStr">
+        <is>
+          <t>Valv.Servic. Succión7/8"-0151R00080-----</t>
+        </is>
+      </c>
+      <c r="C3666" t="n">
+        <v>86354.75</v>
+      </c>
+      <c r="D3666" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910649</t>
+        </is>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>908902</t>
+        </is>
+      </c>
+      <c r="B3667" t="inlineStr">
+        <is>
+          <t>Y-Branch IDUs FQG-B1350A 73 a 135 kW</t>
+        </is>
+      </c>
+      <c r="C3667" t="n">
+        <v>159773.6</v>
+      </c>
+      <c r="D3667" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908902</t>
+        </is>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>990008</t>
+        </is>
+      </c>
+      <c r="B3668" t="inlineStr">
+        <is>
+          <t>Buffer tanque agua BFS-200 s/calen elctr</t>
+        </is>
+      </c>
+      <c r="C3668" t="n">
+        <v>1220323.5</v>
+      </c>
+      <c r="D3668" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>917538</t>
+        </is>
+      </c>
+      <c r="B3669" t="inlineStr">
+        <is>
+          <t>Trafo Evap.09H 220H/10.5v.-20230090A099-</t>
+        </is>
+      </c>
+      <c r="C3669" t="n">
+        <v>26855.15</v>
+      </c>
+      <c r="D3669" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917538</t>
+        </is>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>917963</t>
+        </is>
+      </c>
+      <c r="B3670" t="inlineStr">
+        <is>
+          <t>Motor Cnd.53WCN YDK48-6H-11002012003963-</t>
+        </is>
+      </c>
+      <c r="C3670" t="n">
+        <v>88917</v>
+      </c>
+      <c r="D3670" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917963</t>
+        </is>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>906124</t>
+        </is>
+      </c>
+      <c r="B3671" t="inlineStr">
+        <is>
+          <t>Paleta rotativa para bomba BlueStar-----</t>
+        </is>
+      </c>
+      <c r="C3671" t="n">
+        <v>5124.5</v>
+      </c>
+      <c r="D3671" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>942955</t>
+        </is>
+      </c>
+      <c r="B3672" t="inlineStr">
+        <is>
+          <t>Caño Sal.Evap.3/8F SEC002-000026(BS11IN-</t>
+        </is>
+      </c>
+      <c r="C3672" t="n">
+        <v>18074.25</v>
+      </c>
+      <c r="D3672" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942955</t>
+        </is>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>999138</t>
+        </is>
+      </c>
+      <c r="B3673" t="inlineStr">
+        <is>
+          <t>MTB36HR Evap.3Tr S:0007 Instalada-------</t>
+        </is>
+      </c>
+      <c r="C3673" t="n">
+        <v>358091.75</v>
+      </c>
+      <c r="D3673" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999138</t>
+        </is>
+      </c>
+    </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>955621</t>
+        </is>
+      </c>
+      <c r="B3674" t="inlineStr">
+        <is>
+          <t>Term.dig. ROBERTSHAW RS8110-1eF/C-GBE---</t>
+        </is>
+      </c>
+      <c r="C3674" t="n">
+        <v>74513</v>
+      </c>
+      <c r="D3674" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/955621</t>
+        </is>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>937127</t>
+        </is>
+      </c>
+      <c r="B3675" t="inlineStr">
+        <is>
+          <t>PCB Assembly,Sub EBR74801101</t>
+        </is>
+      </c>
+      <c r="C3675" t="n">
+        <v>55427.7</v>
+      </c>
+      <c r="D3675" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937127</t>
+        </is>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>920820</t>
+        </is>
+      </c>
+      <c r="B3676" t="inlineStr">
+        <is>
+          <t>Pico para Soldar BlueStar HT-1S-c/encend</t>
+        </is>
+      </c>
+      <c r="C3676" t="n">
+        <v>35996.15</v>
+      </c>
+      <c r="D3676" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/920820</t>
+        </is>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>908903</t>
+        </is>
+      </c>
+      <c r="B3677" t="inlineStr">
+        <is>
+          <t>Y-Branch IDUs FQG-B2040A 135 a 204 kW</t>
+        </is>
+      </c>
+      <c r="C3677" t="n">
+        <v>351499.15</v>
+      </c>
+      <c r="D3677" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908903</t>
+        </is>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>962620</t>
+        </is>
+      </c>
+      <c r="B3678" t="inlineStr">
+        <is>
+          <t>Termometro digital 14CF3W-- -50a120C----</t>
+        </is>
+      </c>
+      <c r="C3678" t="n">
+        <v>12963.6</v>
+      </c>
+      <c r="D3678" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/962620</t>
+        </is>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>917557</t>
+        </is>
+      </c>
+      <c r="B3679" t="inlineStr">
+        <is>
+          <t>Trafo Evap.18H-220/14.5v--202300900095--</t>
+        </is>
+      </c>
+      <c r="C3679" t="n">
+        <v>28198.6</v>
+      </c>
+      <c r="D3679" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917557</t>
+        </is>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>906104</t>
+        </is>
+      </c>
+      <c r="B3680" t="inlineStr">
+        <is>
+          <t>Bomba Vacio"BlueStar"VP230 71 L/min--2et</t>
+        </is>
+      </c>
+      <c r="C3680" t="n">
+        <v>176781.4</v>
+      </c>
+      <c r="D3680" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906104</t>
+        </is>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>906510</t>
+        </is>
+      </c>
+      <c r="B3681" t="inlineStr">
+        <is>
+          <t>Motoc."BlueStar"1/6 -ADW51 -R134-125W---</t>
+        </is>
+      </c>
+      <c r="C3681" t="n">
+        <v>53350.2</v>
+      </c>
+      <c r="D3681" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906510</t>
+        </is>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>906480</t>
+        </is>
+      </c>
+      <c r="B3682" t="inlineStr">
+        <is>
+          <t>Mot.Alum.BlueStar 1/8 AL-ADW43-R134-110W</t>
+        </is>
+      </c>
+      <c r="C3682" t="n">
+        <v>45414.15</v>
+      </c>
+      <c r="D3682" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906480</t>
+        </is>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>491208</t>
+        </is>
+      </c>
+      <c r="B3683" t="inlineStr">
+        <is>
+          <t>F.cobre 10g.N*8-BlueStar-mol.ch.134FD10F</t>
+        </is>
+      </c>
+      <c r="C3683" t="n">
+        <v>1897.45</v>
+      </c>
+      <c r="D3683" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/491208</t>
+        </is>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>999015</t>
+        </is>
+      </c>
+      <c r="B3684" t="inlineStr">
+        <is>
+          <t>U.E.TADIRAN ALPHA INV 09A DETALLES 0116-</t>
+        </is>
+      </c>
+      <c r="C3684" t="n">
+        <v>53987.3</v>
+      </c>
+      <c r="D3684" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999015</t>
+        </is>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>917964</t>
+        </is>
+      </c>
+      <c r="B3685" t="inlineStr">
+        <is>
+          <t>Motor Cnd.62WCN YDK55-6H-11002012003327-</t>
+        </is>
+      </c>
+      <c r="C3685" t="n">
+        <v>95038.7</v>
+      </c>
+      <c r="D3685" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917964</t>
+        </is>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>782102</t>
+        </is>
+      </c>
+      <c r="B3686" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 2x4mm-----------</t>
+        </is>
+      </c>
+      <c r="C3686" t="n">
+        <v>254604</v>
+      </c>
+      <c r="D3686" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782102</t>
+        </is>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>994493</t>
+        </is>
+      </c>
+      <c r="B3687" t="inlineStr">
+        <is>
+          <t>Bobina valv.SANHUA PQ-M24012-000007-----</t>
+        </is>
+      </c>
+      <c r="C3687" t="n">
+        <v>38212.15</v>
+      </c>
+      <c r="D3687" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994493</t>
+        </is>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>510100</t>
+        </is>
+      </c>
+      <c r="B3688" t="inlineStr">
+        <is>
+          <t>Capacitor -72-88 mf-110V----------------</t>
+        </is>
+      </c>
+      <c r="C3688" t="n">
+        <v>2423.75</v>
+      </c>
+      <c r="D3688" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/510100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>976371</t>
+        </is>
+      </c>
+      <c r="B3689" t="inlineStr">
+        <is>
+          <t>Detector ELITECH CP-6000-secuencia/falta</t>
+        </is>
+      </c>
+      <c r="C3689" t="n">
+        <v>77712.35000000001</v>
+      </c>
+      <c r="D3689" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/976371</t>
+        </is>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>200608</t>
+        </is>
+      </c>
+      <c r="B3690" t="inlineStr">
+        <is>
+          <t>Terminal pala hembra-TZH--------N*436---</t>
+        </is>
+      </c>
+      <c r="C3690" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="D3690" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/200608</t>
+        </is>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>946010</t>
+        </is>
+      </c>
+      <c r="B3691" t="inlineStr">
+        <is>
+          <t>Mot.Rotat.GMCC 2275fr R22 PH165X1C-4DZD2</t>
+        </is>
+      </c>
+      <c r="C3691" t="n">
+        <v>107988.45</v>
+      </c>
+      <c r="D3691" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/946010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>300100</t>
+        </is>
+      </c>
+      <c r="B3692" t="inlineStr">
+        <is>
+          <t>Cinta aisl.TACSA PVC 10m Blan 15Plus----</t>
+        </is>
+      </c>
+      <c r="C3692" t="n">
+        <v>831</v>
+      </c>
+      <c r="D3692" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/300100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>906618</t>
+        </is>
+      </c>
+      <c r="B3693" t="inlineStr">
+        <is>
+          <t>Evap.BlueStar DL2.0/10 1HP c/desc.1Vx350</t>
+        </is>
+      </c>
+      <c r="C3693" t="n">
+        <v>374074.65</v>
+      </c>
+      <c r="D3693" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906618</t>
+        </is>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>998020</t>
+        </is>
+      </c>
+      <c r="B3694" t="inlineStr">
+        <is>
+          <t>Motocomp.--OFERTA--1345Y-R134-SIN ACCE.6</t>
+        </is>
+      </c>
+      <c r="C3694" t="n">
+        <v>77670.8</v>
+      </c>
+      <c r="D3694" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/998020</t>
+        </is>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>979204</t>
+        </is>
+      </c>
+      <c r="B3695" t="inlineStr">
+        <is>
+          <t>U.C. ATOM TA-V36WDHN1(AtB) 10kW---------</t>
+        </is>
+      </c>
+      <c r="C3695" t="n">
+        <v>1515910.2</v>
+      </c>
+      <c r="D3695" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979204</t>
+        </is>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" t="inlineStr">
+        <is>
+          <t>982323</t>
+        </is>
+      </c>
+      <c r="B3696" t="inlineStr">
+        <is>
+          <t>Cortina "TADIRAN" RM-1209N 0,9Mts F/S---</t>
+        </is>
+      </c>
+      <c r="C3696" t="n">
+        <v>385847.15</v>
+      </c>
+      <c r="D3696" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/982323</t>
+        </is>
+      </c>
+    </row>
+    <row r="3697">
+      <c r="A3697" t="inlineStr">
+        <is>
+          <t>942957</t>
+        </is>
+      </c>
+      <c r="B3697" t="inlineStr">
+        <is>
+          <t>Caño Ent.Evap.1/4F SEC001-000026(BS11IN-</t>
+        </is>
+      </c>
+      <c r="C3697" t="n">
+        <v>18074.25</v>
+      </c>
+      <c r="D3697" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942957</t>
+        </is>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" t="inlineStr">
+        <is>
+          <t>477115</t>
+        </is>
+      </c>
+      <c r="B3698" t="inlineStr">
+        <is>
+          <t>Filtro cobre A.Acond-------1/2 x 1/2----</t>
+        </is>
+      </c>
+      <c r="C3698" t="n">
+        <v>6855.75</v>
+      </c>
+      <c r="D3698" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/477115</t>
+        </is>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" t="inlineStr">
+        <is>
+          <t>960471</t>
+        </is>
+      </c>
+      <c r="B3699" t="inlineStr">
+        <is>
+          <t>Filtro DANFOSS DML032-1/4f------023Z5035</t>
+        </is>
+      </c>
+      <c r="C3699" t="n">
+        <v>20304.1</v>
+      </c>
+      <c r="D3699" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960471</t>
+        </is>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" t="inlineStr">
+        <is>
+          <t>332100</t>
+        </is>
+      </c>
+      <c r="B3700" t="inlineStr">
+        <is>
+          <t>S.copa de 65mm+Ext 320mm+Broca-BlueStar-</t>
+        </is>
+      </c>
+      <c r="C3700" t="n">
+        <v>16800.05</v>
+      </c>
+      <c r="D3700" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/332100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" t="inlineStr">
+        <is>
+          <t>911010</t>
+        </is>
+      </c>
+      <c r="B3701" t="inlineStr">
+        <is>
+          <t>Par de mensulas M420 -Epoxi-------70Kg--</t>
+        </is>
+      </c>
+      <c r="C3701" t="n">
+        <v>9182.549999999999</v>
+      </c>
+      <c r="D3701" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" t="inlineStr">
+        <is>
+          <t>960912</t>
+        </is>
+      </c>
+      <c r="B3702" t="inlineStr">
+        <is>
+          <t>Control nivel DANFOSS TEVA20-5-15000frig</t>
+        </is>
+      </c>
+      <c r="C3702" t="n">
+        <v>94332.35000000001</v>
+      </c>
+      <c r="D3702" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960912</t>
+        </is>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" t="inlineStr">
+        <is>
+          <t>999286</t>
+        </is>
+      </c>
+      <c r="B3703" t="inlineStr">
+        <is>
+          <t>Int.Multi-AMNH186BHAO B/S -</t>
+        </is>
+      </c>
+      <c r="C3703" t="n">
+        <v>706723.95</v>
+      </c>
+      <c r="D3703" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999286</t>
+        </is>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" t="inlineStr">
+        <is>
+          <t>917559</t>
+        </is>
+      </c>
+      <c r="B3704" t="inlineStr">
+        <is>
+          <t>Turbina(TKS18)D100-L682-8101164---------</t>
+        </is>
+      </c>
+      <c r="C3704" t="n">
+        <v>43405.9</v>
+      </c>
+      <c r="D3704" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917559</t>
+        </is>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" t="inlineStr">
+        <is>
+          <t>927600</t>
+        </is>
+      </c>
+      <c r="B3705" t="inlineStr">
+        <is>
+          <t>Varilla ARGENTA SOLDARGEN 100-0--Co.Cb.-</t>
+        </is>
+      </c>
+      <c r="C3705" t="n">
+        <v>844.85</v>
+      </c>
+      <c r="D3705" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/927600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" t="inlineStr">
+        <is>
+          <t>942000</t>
+        </is>
+      </c>
+      <c r="B3706" t="inlineStr">
+        <is>
+          <t>Portatil TADIRAN TAC-12CHPA F/C 220 WiFi</t>
+        </is>
+      </c>
+      <c r="C3706" t="n">
+        <v>511362.45</v>
+      </c>
+      <c r="D3706" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" t="inlineStr">
+        <is>
+          <t>979700</t>
+        </is>
+      </c>
+      <c r="B3707" t="inlineStr">
+        <is>
+          <t>Scanner Dr Smart MIDEA  17222000A55927--</t>
+        </is>
+      </c>
+      <c r="C3707" t="n">
+        <v>125522.55</v>
+      </c>
+      <c r="D3707" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" t="inlineStr">
+        <is>
+          <t>976906</t>
+        </is>
+      </c>
+      <c r="B3708" t="inlineStr">
+        <is>
+          <t>Tablero Elitech ECB1000P-220--3HP-WIFI--</t>
+        </is>
+      </c>
+      <c r="C3708" t="n">
+        <v>196670</v>
+      </c>
+      <c r="D3708" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/976906</t>
+        </is>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" t="inlineStr">
+        <is>
+          <t>955622</t>
+        </is>
+      </c>
+      <c r="B3709" t="inlineStr">
+        <is>
+          <t>Term.dig. ROBERTSHAW RS9110-------------</t>
+        </is>
+      </c>
+      <c r="C3709" t="n">
+        <v>77283</v>
+      </c>
+      <c r="D3709" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/955622</t>
+        </is>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" t="inlineStr">
+        <is>
+          <t>938500</t>
+        </is>
+      </c>
+      <c r="B3710" t="inlineStr">
+        <is>
+          <t>Termota.TADIRAN RSJ15190F 190L c/res.3Kw</t>
+        </is>
+      </c>
+      <c r="C3710" t="n">
+        <v>1669756</v>
+      </c>
+      <c r="D3710" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" t="inlineStr">
+        <is>
+          <t>949700</t>
+        </is>
+      </c>
+      <c r="B3711" t="inlineStr">
+        <is>
+          <t>Motovent.WEIGUANG-BS-4E-250S--aspir.mono</t>
+        </is>
+      </c>
+      <c r="C3711" t="n">
+        <v>57255.9</v>
+      </c>
+      <c r="D3711" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/949700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" t="inlineStr">
+        <is>
+          <t>914999</t>
+        </is>
+      </c>
+      <c r="B3712" t="inlineStr">
+        <is>
+          <t>Contactor ABB--B6-40-00-220V-----------</t>
+        </is>
+      </c>
+      <c r="C3712" t="n">
+        <v>11550.9</v>
+      </c>
+      <c r="D3712" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/914999</t>
+        </is>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" t="inlineStr">
+        <is>
+          <t>960991</t>
+        </is>
+      </c>
+      <c r="B3713" t="inlineStr">
+        <is>
+          <t>Contacto aux.NC p/CI6-50 DANFOSS-37H0112</t>
+        </is>
+      </c>
+      <c r="C3713" t="n">
+        <v>13476.05</v>
+      </c>
+      <c r="D3713" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960991</t>
+        </is>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" t="inlineStr">
+        <is>
+          <t>477330</t>
+        </is>
+      </c>
+      <c r="B3714" t="inlineStr">
+        <is>
+          <t>Conj.biela/per/pist.Embr-FF6----1/5-1001</t>
+        </is>
+      </c>
+      <c r="C3714" t="n">
+        <v>1454.25</v>
+      </c>
+      <c r="D3714" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/477330</t>
+        </is>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" t="inlineStr">
+        <is>
+          <t>576502</t>
+        </is>
+      </c>
+      <c r="B3715" t="inlineStr">
+        <is>
+          <t>Motoc.TECUMSEH 2HP-M404-AWS4522ZXN-mon.I</t>
+        </is>
+      </c>
+      <c r="C3715" t="n">
+        <v>950941</v>
+      </c>
+      <c r="D3715" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/576502</t>
+        </is>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="inlineStr">
+        <is>
+          <t>942810</t>
+        </is>
+      </c>
+      <c r="B3716" t="inlineStr">
+        <is>
+          <t>Sensor TH1/2  92007-005463 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3716" t="n">
+        <v>3573.3</v>
+      </c>
+      <c r="D3716" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942810</t>
+        </is>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" t="inlineStr">
+        <is>
+          <t>936124</t>
+        </is>
+      </c>
+      <c r="B3717" t="inlineStr">
+        <is>
+          <t>UC"ARTCOOL"DUAL-INV"S4-W12JARPA-3520W-FC</t>
+        </is>
+      </c>
+      <c r="C3717" t="n">
+        <v>765187.6899999999</v>
+      </c>
+      <c r="D3717" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/936124</t>
+        </is>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" t="inlineStr">
+        <is>
+          <t>994560</t>
+        </is>
+      </c>
+      <c r="B3718" t="inlineStr">
+        <is>
+          <t>Valv.Termost.SANHUA RFGB01E 0.35TR-R22--</t>
+        </is>
+      </c>
+      <c r="C3718" t="n">
+        <v>37131.85</v>
+      </c>
+      <c r="D3718" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994560</t>
+        </is>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" t="inlineStr">
+        <is>
+          <t>853010</t>
+        </is>
+      </c>
+      <c r="B3719" t="inlineStr">
+        <is>
+          <t>Sensor Evp. TH1/2-5/5k 10104-100014</t>
+        </is>
+      </c>
+      <c r="C3719" t="n">
+        <v>6731.1</v>
+      </c>
+      <c r="D3719" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/853010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" t="inlineStr">
+        <is>
+          <t>906642</t>
+        </is>
+      </c>
+      <c r="B3720" t="inlineStr">
+        <is>
+          <t>Evap.BlueStar DD1.3/7 1.5HPc/desc.1Vx350</t>
+        </is>
+      </c>
+      <c r="C3720" t="n">
+        <v>445305.2</v>
+      </c>
+      <c r="D3720" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906642</t>
+        </is>
+      </c>
+    </row>
+    <row r="3721">
+      <c r="A3721" t="inlineStr">
+        <is>
+          <t>962646</t>
+        </is>
+      </c>
+      <c r="B3721" t="inlineStr">
+        <is>
+          <t>Detector de Fuga BlueStar CT-CPU06------</t>
+        </is>
+      </c>
+      <c r="C3721" t="n">
+        <v>103487.2</v>
+      </c>
+      <c r="D3721" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/962646</t>
+        </is>
+      </c>
+    </row>
+    <row r="3722">
+      <c r="A3722" t="inlineStr">
+        <is>
+          <t>979510</t>
+        </is>
+      </c>
+      <c r="B3722" t="inlineStr">
+        <is>
+          <t>U.E. Hi-wall BLUESTAR MSAFBU-09HRDN8 R32</t>
+        </is>
+      </c>
+      <c r="C3722" t="n">
+        <v>255227.8</v>
+      </c>
+      <c r="D3722" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979510</t>
+        </is>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" t="inlineStr">
+        <is>
+          <t>590100</t>
+        </is>
+      </c>
+      <c r="B3723" t="inlineStr">
+        <is>
+          <t>Filtro WHITE"ECO"35-1/4x3/16 sol.molecul</t>
+        </is>
+      </c>
+      <c r="C3723" t="n">
+        <v>9864.83</v>
+      </c>
+      <c r="D3723" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/590100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" t="inlineStr">
+        <is>
+          <t>961690</t>
+        </is>
+      </c>
+      <c r="B3724" t="inlineStr">
+        <is>
+          <t>Int.placa DANFOSS Ev1,5-Cond 2 -021H1298</t>
+        </is>
+      </c>
+      <c r="C3724" t="n">
+        <v>396816.35</v>
+      </c>
+      <c r="D3724" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/961690</t>
+        </is>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" t="inlineStr">
+        <is>
+          <t>856050</t>
+        </is>
+      </c>
+      <c r="B3725" t="inlineStr">
+        <is>
+          <t>PCB Display TADI35 -1090250119AN (00083)</t>
+        </is>
+      </c>
+      <c r="C3725" t="n">
+        <v>8794.75</v>
+      </c>
+      <c r="D3725" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/856050</t>
+        </is>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" t="inlineStr">
+        <is>
+          <t>937178</t>
+        </is>
+      </c>
+      <c r="B3726" t="inlineStr">
+        <is>
+          <t>PCB Main ARUB/N100/200LN3 - EBR82795402</t>
+        </is>
+      </c>
+      <c r="C3726" t="n">
+        <v>122323.2</v>
+      </c>
+      <c r="D3726" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937178</t>
+        </is>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" t="inlineStr">
+        <is>
+          <t>979310</t>
+        </is>
+      </c>
+      <c r="B3727" t="inlineStr">
+        <is>
+          <t>Control Remoto RM12F</t>
+        </is>
+      </c>
+      <c r="C3727" t="n">
+        <v>40483.55</v>
+      </c>
+      <c r="D3727" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979310</t>
+        </is>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" t="inlineStr">
+        <is>
+          <t>495902</t>
+        </is>
+      </c>
+      <c r="B3728" t="inlineStr">
+        <is>
+          <t>Term.MACO TS1525-3A--amb.inver. -25a15*-</t>
+        </is>
+      </c>
+      <c r="C3728" t="n">
+        <v>1565.05</v>
+      </c>
+      <c r="D3728" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/495902</t>
+        </is>
+      </c>
+    </row>
+    <row r="3729">
+      <c r="A3729" t="inlineStr">
+        <is>
+          <t>140358</t>
+        </is>
+      </c>
+      <c r="B3729" t="inlineStr">
+        <is>
+          <t>Rollo 25x1mx5mm-"ISOLANT"--Estandar--E5-</t>
+        </is>
+      </c>
+      <c r="C3729" t="n">
+        <v>830.36</v>
+      </c>
+      <c r="D3729" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/140358</t>
+        </is>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" t="inlineStr">
+        <is>
+          <t>960616</t>
+        </is>
+      </c>
+      <c r="B3730" t="inlineStr">
+        <is>
+          <t>Presost.DANFOSS--KPI35-0.2/8bar-0601217-</t>
+        </is>
+      </c>
+      <c r="C3730" t="n">
+        <v>249978.65</v>
+      </c>
+      <c r="D3730" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960616</t>
+        </is>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" t="inlineStr">
+        <is>
+          <t>937402</t>
+        </is>
+      </c>
+      <c r="B3731" t="inlineStr">
+        <is>
+          <t>Turbina 5901AR2441Q - TSNH1865DA0</t>
+        </is>
+      </c>
+      <c r="C3731" t="n">
+        <v>45497.25</v>
+      </c>
+      <c r="D3731" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937402</t>
+        </is>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" t="inlineStr">
+        <is>
+          <t>913708</t>
+        </is>
+      </c>
+      <c r="B3732" t="inlineStr">
+        <is>
+          <t>Sella Fuga A/A EXTREME 12ml--TR1062L01S2</t>
+        </is>
+      </c>
+      <c r="C3732" t="n">
+        <v>10636.8</v>
+      </c>
+      <c r="D3732" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913708</t>
+        </is>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="inlineStr">
+        <is>
+          <t>165002</t>
+        </is>
+      </c>
+      <c r="B3733" t="inlineStr">
+        <is>
+          <t>Mot.401717-1/3-M-SURREY-FA4366-Rx:FA4403</t>
+        </is>
+      </c>
+      <c r="C3733" t="n">
+        <v>443560.1</v>
+      </c>
+      <c r="D3733" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/165002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="inlineStr">
+        <is>
+          <t>255502</t>
+        </is>
+      </c>
+      <c r="B3734" t="inlineStr">
+        <is>
+          <t>Termota.LG R5TT27F-SA0 270L HeatPump 2kW</t>
+        </is>
+      </c>
+      <c r="C3734" t="n">
+        <v>4660137.2</v>
+      </c>
+      <c r="D3734" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/255502</t>
+        </is>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="inlineStr">
+        <is>
+          <t>284000</t>
+        </is>
+      </c>
+      <c r="B3735" t="inlineStr">
+        <is>
+          <t>Dispenser 02P-RED-F/C USHUAIA-c/filtro--</t>
+        </is>
+      </c>
+      <c r="C3735" t="n">
+        <v>434640.7</v>
+      </c>
+      <c r="D3735" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/284000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="inlineStr">
+        <is>
+          <t>488101</t>
+        </is>
+      </c>
+      <c r="B3736" t="inlineStr">
+        <is>
+          <t>Bolsa 100 Prec.PTFL4-200-200mmx4.6mm-NEG</t>
+        </is>
+      </c>
+      <c r="C3736" t="n">
+        <v>4293.5</v>
+      </c>
+      <c r="D3736" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/488101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>913679</t>
+        </is>
+      </c>
+      <c r="B3737" t="inlineStr">
+        <is>
+          <t>Sellador de fuga EXTERNAL past.TR116601-</t>
+        </is>
+      </c>
+      <c r="C3737" t="n">
+        <v>11717.1</v>
+      </c>
+      <c r="D3737" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913679</t>
+        </is>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>913664</t>
+        </is>
+      </c>
+      <c r="B3738" t="inlineStr">
+        <is>
+          <t>Detec.Fug.TRACE-BRILLIANT 1x60-TR1133EJ9</t>
+        </is>
+      </c>
+      <c r="C3738" t="n">
+        <v>16689.25</v>
+      </c>
+      <c r="D3738" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913664</t>
+        </is>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="inlineStr">
+        <is>
+          <t>390770</t>
+        </is>
+      </c>
+      <c r="B3739" t="inlineStr">
+        <is>
+          <t>Junta DANFOSS alta-------------915-G7882</t>
+        </is>
+      </c>
+      <c r="C3739" t="n">
+        <v>152.35</v>
+      </c>
+      <c r="D3739" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/390770</t>
+        </is>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="inlineStr">
+        <is>
+          <t>575341</t>
+        </is>
+      </c>
+      <c r="B3740" t="inlineStr">
+        <is>
+          <t>Mot. EMBRACO-1/2+B22-NE2134-T2155-Monof-</t>
+        </is>
+      </c>
+      <c r="C3740" t="n">
+        <v>222583.35</v>
+      </c>
+      <c r="D3740" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/575341</t>
+        </is>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="inlineStr">
+        <is>
+          <t>400420</t>
+        </is>
+      </c>
+      <c r="B3741" t="inlineStr">
+        <is>
+          <t>Manija 2294 Exterior pta. Superpuesta</t>
+        </is>
+      </c>
+      <c r="C3741" t="n">
+        <v>18794.45</v>
+      </c>
+      <c r="D3741" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/400420</t>
+        </is>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="inlineStr">
+        <is>
+          <t>971046</t>
+        </is>
+      </c>
+      <c r="B3742" t="inlineStr">
+        <is>
+          <t>Manov.BlueStar-1527L-baja-R410-------d80</t>
+        </is>
+      </c>
+      <c r="C3742" t="n">
+        <v>7548.25</v>
+      </c>
+      <c r="D3742" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/971046</t>
+        </is>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="inlineStr">
+        <is>
+          <t>940612</t>
+        </is>
+      </c>
+      <c r="B3743" t="inlineStr">
+        <is>
+          <t>Balanza  Digital  VALUE-VES50A-cap:50Kg-</t>
+        </is>
+      </c>
+      <c r="C3743" t="n">
+        <v>190174.35</v>
+      </c>
+      <c r="D3743" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/940612</t>
+        </is>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="inlineStr">
+        <is>
+          <t>914140</t>
+        </is>
+      </c>
+      <c r="B3744" t="inlineStr">
+        <is>
+          <t>UC."BLUESTAR"INVERTER BS11INV-2500FC R32</t>
+        </is>
+      </c>
+      <c r="C3744" t="n">
+        <v>400558.83</v>
+      </c>
+      <c r="D3744" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/914140</t>
+        </is>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>906664</t>
+        </is>
+      </c>
+      <c r="B3745" t="inlineStr">
+        <is>
+          <t>Cond.BlueStar FNF1.3/4.4  1/3HP -p/1v250</t>
+        </is>
+      </c>
+      <c r="C3745" t="n">
+        <v>71452.14999999999</v>
+      </c>
+      <c r="D3745" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906664</t>
+        </is>
+      </c>
+    </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>174549</t>
+        </is>
+      </c>
+      <c r="B3746" t="inlineStr">
+        <is>
+          <t>Balde 10kg.desincrus.ACID CRUST b.acida-</t>
+        </is>
+      </c>
+      <c r="C3746" t="n">
+        <v>31330.6</v>
+      </c>
+      <c r="D3746" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/174549</t>
+        </is>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="inlineStr">
+        <is>
+          <t>906562</t>
+        </is>
+      </c>
+      <c r="B3747" t="inlineStr">
+        <is>
+          <t>Motoc.BlueStar 1/5 MLGQR45K-B404--------</t>
+        </is>
+      </c>
+      <c r="C3747" t="n">
+        <v>84512.7</v>
+      </c>
+      <c r="D3747" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906562</t>
+        </is>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="inlineStr">
+        <is>
+          <t>913602</t>
+        </is>
+      </c>
+      <c r="B3748" t="inlineStr">
+        <is>
+          <t>Limpia Evap.Purif.EVO TABS 18PZ.AB108901</t>
+        </is>
+      </c>
+      <c r="C3748" t="n">
+        <v>65898.3</v>
+      </c>
+      <c r="D3748" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913602</t>
+        </is>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>225102</t>
+        </is>
+      </c>
+      <c r="B3749" t="inlineStr">
+        <is>
+          <t>Valv.termost."ALCO"F12-TCLE1  1tn-FC----</t>
+        </is>
+      </c>
+      <c r="C3749" t="n">
+        <v>70358</v>
+      </c>
+      <c r="D3749" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/225102</t>
+        </is>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="inlineStr">
+        <is>
+          <t>174485</t>
+        </is>
+      </c>
+      <c r="B3750" t="inlineStr">
+        <is>
+          <t>Balde 5lts.-L.D.V.-Desodorante p/conduc.</t>
+        </is>
+      </c>
+      <c r="C3750" t="n">
+        <v>17769.76</v>
+      </c>
+      <c r="D3750" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/174485</t>
+        </is>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="inlineStr">
+        <is>
+          <t>398395</t>
+        </is>
+      </c>
+      <c r="B3751" t="inlineStr">
+        <is>
+          <t>Rollo TADIRAN-PERT II-16X2mm ROJO 400m--</t>
+        </is>
+      </c>
+      <c r="C3751" t="n">
+        <v>253039.5</v>
+      </c>
+      <c r="D3751" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/398395</t>
+        </is>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="inlineStr">
+        <is>
+          <t>745000</t>
+        </is>
+      </c>
+      <c r="B3752" t="inlineStr">
+        <is>
+          <t>Caldera"ITALTHERM"c/Intercamb 90x3kW----</t>
+        </is>
+      </c>
+      <c r="C3752" t="n">
+        <v>65174499</v>
+      </c>
+      <c r="D3752" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/745000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="inlineStr">
+        <is>
+          <t>472303</t>
+        </is>
+      </c>
+      <c r="B3753" t="inlineStr">
+        <is>
+          <t>Curvas de cobre R.LARGO---1/4-C-90*-----</t>
+        </is>
+      </c>
+      <c r="C3753" t="n">
+        <v>706.35</v>
+      </c>
+      <c r="D3753" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/472303</t>
+        </is>
+      </c>
+    </row>
+    <row r="3754">
+      <c r="A3754" t="inlineStr">
+        <is>
+          <t>913630</t>
+        </is>
+      </c>
+      <c r="B3754" t="inlineStr">
+        <is>
+          <t>BELNET AEROS.750ml.cono  141B-TR1009YWM0</t>
+        </is>
+      </c>
+      <c r="C3754" t="n">
+        <v>17243.25</v>
+      </c>
+      <c r="D3754" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913630</t>
+        </is>
+      </c>
+    </row>
+    <row r="3755">
+      <c r="A3755" t="inlineStr">
+        <is>
+          <t>745250</t>
+        </is>
+      </c>
+      <c r="B3755" t="inlineStr">
+        <is>
+          <t>PRENSAESTOPA D.21              532000140</t>
+        </is>
+      </c>
+      <c r="C3755" t="n">
+        <v>2229.85</v>
+      </c>
+      <c r="D3755" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/745250</t>
+        </is>
+      </c>
+    </row>
+    <row r="3756">
+      <c r="A3756" t="inlineStr">
+        <is>
+          <t>893900</t>
+        </is>
+      </c>
+      <c r="B3756" t="inlineStr">
+        <is>
+          <t>Sensor de Caudal Nepto D003200374</t>
+        </is>
+      </c>
+      <c r="C3756" t="n">
+        <v>12672.75</v>
+      </c>
+      <c r="D3756" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/893900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3757">
+      <c r="A3757" t="inlineStr">
+        <is>
+          <t>913608</t>
+        </is>
+      </c>
+      <c r="B3757" t="inlineStr">
+        <is>
+          <t>Protect.Anticorr.NO AGE 1LT.AB1100K01---</t>
+        </is>
+      </c>
+      <c r="C3757" t="n">
+        <v>14570.2</v>
+      </c>
+      <c r="D3757" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913608</t>
+        </is>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="inlineStr">
+        <is>
+          <t>240100</t>
+        </is>
+      </c>
+      <c r="B3758" t="inlineStr">
+        <is>
+          <t>Frente compacto GOLDSTAR/HITACHI--------</t>
+        </is>
+      </c>
+      <c r="C3758" t="n">
+        <v>2603.8</v>
+      </c>
+      <c r="D3758" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3759">
+      <c r="A3759" t="inlineStr">
+        <is>
+          <t>965005</t>
+        </is>
+      </c>
+      <c r="B3759" t="inlineStr">
+        <is>
+          <t>Valv.term.SPORLAN-NIF-1/4ton-F12-s/comp-</t>
+        </is>
+      </c>
+      <c r="C3759" t="n">
+        <v>35179</v>
+      </c>
+      <c r="D3759" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/965005</t>
+        </is>
+      </c>
+    </row>
+    <row r="3760">
+      <c r="A3760" t="inlineStr">
+        <is>
+          <t>937170</t>
+        </is>
+      </c>
+      <c r="B3760" t="inlineStr">
+        <is>
+          <t>PCB Assembly 6871A20912G</t>
+        </is>
+      </c>
+      <c r="C3760" t="n">
+        <v>60898.45</v>
+      </c>
+      <c r="D3760" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937170</t>
+        </is>
+      </c>
+    </row>
+    <row r="3761">
+      <c r="A3761" t="inlineStr">
+        <is>
+          <t>913615</t>
+        </is>
+      </c>
+      <c r="B3761" t="inlineStr">
+        <is>
+          <t>T/fug.STOPUP Servo direc 250ml-TR1144QP2</t>
+        </is>
+      </c>
+      <c r="C3761" t="n">
+        <v>10415.2</v>
+      </c>
+      <c r="D3761" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913615</t>
+        </is>
+      </c>
+    </row>
+    <row r="3762">
+      <c r="A3762" t="inlineStr">
+        <is>
+          <t>979980</t>
+        </is>
+      </c>
+      <c r="B3762" t="inlineStr">
+        <is>
+          <t>PCB Ppal.Ignición 17127600000708(TGS)</t>
+        </is>
+      </c>
+      <c r="C3762" t="n">
+        <v>176726</v>
+      </c>
+      <c r="D3762" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979980</t>
+        </is>
+      </c>
+    </row>
+    <row r="3763">
+      <c r="A3763" t="inlineStr">
+        <is>
+          <t>576330</t>
+        </is>
+      </c>
+      <c r="B3763" t="inlineStr">
+        <is>
+          <t>U.Cond TAURI 2HP B404 UTS0152LZHF2XN0-1F</t>
+        </is>
+      </c>
+      <c r="C3763" t="n">
+        <v>1465288.45</v>
+      </c>
+      <c r="D3763" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/576330</t>
+        </is>
+      </c>
+    </row>
+    <row r="3764">
+      <c r="A3764" t="inlineStr">
+        <is>
+          <t>979987</t>
+        </is>
+      </c>
+      <c r="B3764" t="inlineStr">
+        <is>
+          <t>PCB Inverter 17123000008517 (TOVA36)</t>
+        </is>
+      </c>
+      <c r="C3764" t="n">
+        <v>873990.4</v>
+      </c>
+      <c r="D3764" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979987</t>
+        </is>
+      </c>
+    </row>
+    <row r="3765">
+      <c r="A3765" t="inlineStr">
+        <is>
+          <t>565000</t>
+        </is>
+      </c>
+      <c r="B3765" t="inlineStr">
+        <is>
+          <t>Llave ROTALOCK 1.1/4 de 1/4Fx7/8s-(1735)</t>
+        </is>
+      </c>
+      <c r="C3765" t="n">
+        <v>119608.6</v>
+      </c>
+      <c r="D3765" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/565000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3766">
+      <c r="A3766" t="inlineStr">
+        <is>
+          <t>404220</t>
+        </is>
+      </c>
+      <c r="B3766" t="inlineStr">
+        <is>
+          <t>Rollo cortina Cristal 10cmx2mmx50mts-MT-</t>
+        </is>
+      </c>
+      <c r="C3766" t="n">
+        <v>153347.2</v>
+      </c>
+      <c r="D3766" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/404220</t>
+        </is>
+      </c>
+    </row>
+    <row r="3767">
+      <c r="A3767" t="inlineStr">
+        <is>
+          <t>778205</t>
+        </is>
+      </c>
+      <c r="B3767" t="inlineStr">
+        <is>
+          <t>Pico p/soldar c/manguera DTH7-----------</t>
+        </is>
+      </c>
+      <c r="C3767" t="n">
+        <v>126810.6</v>
+      </c>
+      <c r="D3767" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/778205</t>
+        </is>
+      </c>
+    </row>
+    <row r="3768">
+      <c r="A3768" t="inlineStr">
+        <is>
+          <t>965310</t>
+        </is>
+      </c>
+      <c r="B3768" t="inlineStr">
+        <is>
+          <t>Valv.term.SPORLAN DAE5ton-NH3-c/filtro--</t>
+        </is>
+      </c>
+      <c r="C3768" t="n">
+        <v>52768.5</v>
+      </c>
+      <c r="D3768" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/965310</t>
+        </is>
+      </c>
+    </row>
+    <row r="3769">
+      <c r="A3769" t="inlineStr">
+        <is>
+          <t>253000</t>
+        </is>
+      </c>
+      <c r="B3769" t="inlineStr">
+        <is>
+          <t>Mini.Sol.BlueStar-1m tubo alum. certif--</t>
+        </is>
+      </c>
+      <c r="C3769" t="n">
+        <v>1085784.6</v>
+      </c>
+      <c r="D3769" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/253000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3770">
+      <c r="A3770" t="inlineStr">
+        <is>
+          <t>221202</t>
+        </is>
+      </c>
+      <c r="B3770" t="inlineStr">
+        <is>
+          <t>Poliuretano en aerosol-300ml------------</t>
+        </is>
+      </c>
+      <c r="C3770" t="n">
+        <v>7188.15</v>
+      </c>
+      <c r="D3770" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/221202</t>
+        </is>
+      </c>
+    </row>
+    <row r="3771">
+      <c r="A3771" t="inlineStr">
+        <is>
+          <t>962541</t>
+        </is>
+      </c>
+      <c r="B3771" t="inlineStr">
+        <is>
+          <t>Kit Instalacion 1/4+3/8-3mts/rollo------</t>
+        </is>
+      </c>
+      <c r="C3771" t="n">
+        <v>40594.35</v>
+      </c>
+      <c r="D3771" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/962541</t>
+        </is>
+      </c>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="inlineStr">
+        <is>
+          <t>938305</t>
+        </is>
+      </c>
+      <c r="B3772" t="inlineStr">
+        <is>
+          <t>Bomba calor INV 65kW 380 MH-SU65RN8L R32</t>
+        </is>
+      </c>
+      <c r="C3772" t="n">
+        <v>14977902.45</v>
+      </c>
+      <c r="D3772" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/938305</t>
+        </is>
+      </c>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="inlineStr">
+        <is>
+          <t>906004</t>
+        </is>
+      </c>
+      <c r="B3773" t="inlineStr">
+        <is>
+          <t>Tester Digital BlueStar TA801C----------</t>
+        </is>
+      </c>
+      <c r="C3773" t="n">
+        <v>24099</v>
+      </c>
+      <c r="D3773" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906004</t>
+        </is>
+      </c>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="inlineStr">
+        <is>
+          <t>481502</t>
+        </is>
+      </c>
+      <c r="B3774" t="inlineStr">
+        <is>
+          <t>Actuador HONEYWELL ON-OFF M100BG---220V-</t>
+        </is>
+      </c>
+      <c r="C3774" t="n">
+        <v>101243.5</v>
+      </c>
+      <c r="D3774" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/481502</t>
+        </is>
+      </c>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="inlineStr">
+        <is>
+          <t>910651</t>
+        </is>
+      </c>
+      <c r="B3775" t="inlineStr">
+        <is>
+          <t>Acurrator (082) B1789882</t>
+        </is>
+      </c>
+      <c r="C3775" t="n">
+        <v>13226.75</v>
+      </c>
+      <c r="D3775" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910651</t>
+        </is>
+      </c>
+    </row>
+    <row r="3776">
+      <c r="A3776" t="inlineStr">
+        <is>
+          <t>960408</t>
+        </is>
+      </c>
+      <c r="B3776" t="inlineStr">
+        <is>
+          <t>Valv.reg.caudal DANFOSS WVS 50-2"+piloto</t>
+        </is>
+      </c>
+      <c r="C3776" t="n">
+        <v>192515</v>
+      </c>
+      <c r="D3776" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960408</t>
+        </is>
+      </c>
+    </row>
+    <row r="3777">
+      <c r="A3777" t="inlineStr">
+        <is>
+          <t>565910</t>
+        </is>
+      </c>
+      <c r="B3777" t="inlineStr">
+        <is>
+          <t>Union 1/4GMx1/4GM---de bronce------00369</t>
+        </is>
+      </c>
+      <c r="C3777" t="n">
+        <v>5512.3</v>
+      </c>
+      <c r="D3777" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/565910</t>
+        </is>
+      </c>
+    </row>
+    <row r="3778">
+      <c r="A3778" t="inlineStr">
+        <is>
+          <t>907758</t>
+        </is>
+      </c>
+      <c r="B3778" t="inlineStr">
+        <is>
+          <t>Termom."BlueStar" LT-123-(-30a30*C)-----</t>
+        </is>
+      </c>
+      <c r="C3778" t="n">
+        <v>5720.05</v>
+      </c>
+      <c r="D3778" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/907758</t>
+        </is>
+      </c>
+    </row>
+    <row r="3779">
+      <c r="A3779" t="inlineStr">
+        <is>
+          <t>908913</t>
+        </is>
+      </c>
+      <c r="B3779" t="inlineStr">
+        <is>
+          <t>Control inalambrico YR-HRS01</t>
+        </is>
+      </c>
+      <c r="C3779" t="n">
+        <v>19154.55</v>
+      </c>
+      <c r="D3779" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908913</t>
+        </is>
+      </c>
+    </row>
+    <row r="3780">
+      <c r="A3780" t="inlineStr">
+        <is>
+          <t>940800</t>
+        </is>
+      </c>
+      <c r="B3780" t="inlineStr">
+        <is>
+          <t>Caja Value vacia oferta variadas</t>
+        </is>
+      </c>
+      <c r="C3780" t="n">
+        <v>11080</v>
+      </c>
+      <c r="D3780" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/940800</t>
+        </is>
+      </c>
+    </row>
+    <row r="3781">
+      <c r="A3781" t="inlineStr">
+        <is>
+          <t>990010</t>
+        </is>
+      </c>
+      <c r="B3781" t="inlineStr">
+        <is>
+          <t>Calentador electrico 1,5kW</t>
+        </is>
+      </c>
+      <c r="C3781" t="n">
+        <v>44569.3</v>
+      </c>
+      <c r="D3781" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3782">
+      <c r="A3782" t="inlineStr">
+        <is>
+          <t>900812</t>
+        </is>
+      </c>
+      <c r="B3782" t="inlineStr">
+        <is>
+          <t>Main Board TK-H5.5NH 30223000046</t>
+        </is>
+      </c>
+      <c r="C3782" t="n">
+        <v>203428.8</v>
+      </c>
+      <c r="D3782" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/900812</t>
+        </is>
+      </c>
+    </row>
+    <row r="3783">
+      <c r="A3783" t="inlineStr">
+        <is>
+          <t>596586</t>
+        </is>
+      </c>
+      <c r="B3783" t="inlineStr">
+        <is>
+          <t>Frent.Plast.Compacto 660x425------------</t>
+        </is>
+      </c>
+      <c r="C3783" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3783" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/596586</t>
+        </is>
+      </c>
+    </row>
+    <row r="3784">
+      <c r="A3784" t="inlineStr">
+        <is>
+          <t>595000</t>
+        </is>
+      </c>
+      <c r="B3784" t="inlineStr">
+        <is>
+          <t>Turbina MP 110X87 C/B 9.5---------------</t>
+        </is>
+      </c>
+      <c r="C3784" t="n">
+        <v>9916.6</v>
+      </c>
+      <c r="D3784" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/595000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3785">
+      <c r="A3785" t="inlineStr">
+        <is>
+          <t>917589</t>
+        </is>
+      </c>
+      <c r="B3785" t="inlineStr">
+        <is>
+          <t>Trafo Evap.24H-220-9.5/11v-202300900534-</t>
+        </is>
+      </c>
+      <c r="C3785" t="n">
+        <v>40538.95</v>
+      </c>
+      <c r="D3785" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917589</t>
+        </is>
+      </c>
+    </row>
+    <row r="3786">
+      <c r="A3786" t="inlineStr">
+        <is>
+          <t>906126</t>
+        </is>
+      </c>
+      <c r="B3786" t="inlineStr">
+        <is>
+          <t>O-ring para bomba BlueStar--------------</t>
+        </is>
+      </c>
+      <c r="C3786" t="n">
+        <v>5124.5</v>
+      </c>
+      <c r="D3786" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906126</t>
+        </is>
+      </c>
+    </row>
+    <row r="3787">
+      <c r="A3787" t="inlineStr">
+        <is>
+          <t>942959</t>
+        </is>
+      </c>
+      <c r="B3787" t="inlineStr">
+        <is>
+          <t>Caño Ent.Evap.1/4F SEC002-000029(BS11IN-</t>
+        </is>
+      </c>
+      <c r="C3787" t="n">
+        <v>18074.25</v>
+      </c>
+      <c r="D3787" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942959</t>
+        </is>
+      </c>
+    </row>
+    <row r="3788">
+      <c r="A3788" t="inlineStr">
+        <is>
+          <t>955630</t>
+        </is>
+      </c>
+      <c r="B3788" t="inlineStr">
+        <is>
+          <t>Term.prog.ROBERTSHAW RS3110-1eF/C-5+2GBE</t>
+        </is>
+      </c>
+      <c r="C3788" t="n">
+        <v>85953.10000000001</v>
+      </c>
+      <c r="D3788" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/955630</t>
+        </is>
+      </c>
+    </row>
+    <row r="3789">
+      <c r="A3789" t="inlineStr">
+        <is>
+          <t>960939</t>
+        </is>
+      </c>
+      <c r="B3789" t="inlineStr">
+        <is>
+          <t>Int.auto.DANFOSS CTI25M-0.63- 1  A-B3144</t>
+        </is>
+      </c>
+      <c r="C3789" t="n">
+        <v>96257.5</v>
+      </c>
+      <c r="D3789" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960939</t>
+        </is>
+      </c>
+    </row>
+    <row r="3790">
+      <c r="A3790" t="inlineStr">
+        <is>
+          <t>937128</t>
+        </is>
+      </c>
+      <c r="B3790" t="inlineStr">
+        <is>
+          <t>PCB Assembly EBR76886201</t>
+        </is>
+      </c>
+      <c r="C3790" t="n">
+        <v>129455.95</v>
+      </c>
+      <c r="D3790" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937128</t>
+        </is>
+      </c>
+    </row>
+    <row r="3791">
+      <c r="A3791" t="inlineStr">
+        <is>
+          <t>910653</t>
+        </is>
+      </c>
+      <c r="B3791" t="inlineStr">
+        <is>
+          <t>Tapa Metal Caja Ctrol.-121R00053PDG-----</t>
+        </is>
+      </c>
+      <c r="C3791" t="n">
+        <v>118569.85</v>
+      </c>
+      <c r="D3791" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/910653</t>
+        </is>
+      </c>
+    </row>
+    <row r="3792">
+      <c r="A3792" t="inlineStr">
+        <is>
+          <t>908915</t>
+        </is>
+      </c>
+      <c r="B3792" t="inlineStr">
+        <is>
+          <t>Control inalambrico YR-HQS01</t>
+        </is>
+      </c>
+      <c r="C3792" t="n">
+        <v>28752.6</v>
+      </c>
+      <c r="D3792" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908915</t>
+        </is>
+      </c>
+    </row>
+    <row r="3793">
+      <c r="A3793" t="inlineStr">
+        <is>
+          <t>917867</t>
+        </is>
+      </c>
+      <c r="B3793" t="inlineStr">
+        <is>
+          <t>Turbina BGH23 (92x540)p/9---201100200011</t>
+        </is>
+      </c>
+      <c r="C3793" t="n">
+        <v>65898.3</v>
+      </c>
+      <c r="D3793" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/917867</t>
+        </is>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="inlineStr">
+        <is>
+          <t>999025</t>
+        </is>
+      </c>
+      <c r="B3794" t="inlineStr">
+        <is>
+          <t>U.E.ELECTRA TTB72RA ONOFF Instalada 0051</t>
+        </is>
+      </c>
+      <c r="C3794" t="n">
+        <v>774007.25</v>
+      </c>
+      <c r="D3794" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3795">
+      <c r="A3795" t="inlineStr">
+        <is>
+          <t>942921</t>
+        </is>
+      </c>
+      <c r="B3795" t="inlineStr">
+        <is>
+          <t>Multideriv.Caño Evp.SEC003-0008(BS11INV)</t>
+        </is>
+      </c>
+      <c r="C3795" t="n">
+        <v>31564.15</v>
+      </c>
+      <c r="D3795" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942921</t>
+        </is>
+      </c>
+    </row>
+    <row r="3796">
+      <c r="A3796" t="inlineStr">
+        <is>
+          <t>955612</t>
+        </is>
+      </c>
+      <c r="B3796" t="inlineStr">
+        <is>
+          <t>Term.prog.ROBERTSHAW RS1010-1et.FrioSolo</t>
+        </is>
+      </c>
+      <c r="C3796" t="n">
+        <v>55400</v>
+      </c>
+      <c r="D3796" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/955612</t>
+        </is>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="inlineStr">
+        <is>
+          <t>942812</t>
+        </is>
+      </c>
+      <c r="B3797" t="inlineStr">
+        <is>
+          <t>Motor Evap. 19W. - Y5S413A557 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3797" t="n">
+        <v>56577.25</v>
+      </c>
+      <c r="D3797" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942812</t>
+        </is>
+      </c>
+    </row>
+    <row r="3798">
+      <c r="A3798" t="inlineStr">
+        <is>
+          <t>853012</t>
+        </is>
+      </c>
+      <c r="B3798" t="inlineStr">
+        <is>
+          <t>Motor Evap.14w. 22001-000299BS (TA8-32)</t>
+        </is>
+      </c>
+      <c r="C3798" t="n">
+        <v>184634.35</v>
+      </c>
+      <c r="D3798" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/853012</t>
+        </is>
+      </c>
+    </row>
+    <row r="3799">
+      <c r="A3799" t="inlineStr">
+        <is>
+          <t>979512</t>
+        </is>
+      </c>
+      <c r="B3799" t="inlineStr">
+        <is>
+          <t>U.E. Hi-wall BLUESTAR MSAFBU-12HRDNX R32</t>
+        </is>
+      </c>
+      <c r="C3799" t="n">
+        <v>286071.75</v>
+      </c>
+      <c r="D3799" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979512</t>
+        </is>
+      </c>
+    </row>
+    <row r="3800">
+      <c r="A3800" t="inlineStr">
+        <is>
+          <t>937179</t>
+        </is>
+      </c>
+      <c r="B3800" t="inlineStr">
+        <is>
+          <t>PCB Assembly SUB ARNU54GBRA2 EBR57725520</t>
+        </is>
+      </c>
+      <c r="C3800" t="n">
+        <v>1994.4</v>
+      </c>
+      <c r="D3800" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937179</t>
+        </is>
+      </c>
+    </row>
+    <row r="3801">
+      <c r="A3801" t="inlineStr">
+        <is>
+          <t>940815</t>
+        </is>
+      </c>
+      <c r="B3801" t="inlineStr">
+        <is>
+          <t>Pinza Amperometrica VMC-1  VALUE--</t>
+        </is>
+      </c>
+      <c r="C3801" t="n">
+        <v>54222.75</v>
+      </c>
+      <c r="D3801" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/940815</t>
+        </is>
+      </c>
+    </row>
+    <row r="3802">
+      <c r="A3802" t="inlineStr">
+        <is>
+          <t>913603</t>
+        </is>
+      </c>
+      <c r="B3802" t="inlineStr">
+        <is>
+          <t>Unidad limp.Evap Purif.EVO TABS---------</t>
+        </is>
+      </c>
+      <c r="C3802" t="n">
+        <v>3656.4</v>
+      </c>
+      <c r="D3802" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913603</t>
+        </is>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="inlineStr">
+        <is>
+          <t>745002</t>
+        </is>
+      </c>
+      <c r="B3803" t="inlineStr">
+        <is>
+          <t>Caldera"ITALTHERM"c/Intercamb 90x2+115kW</t>
+        </is>
+      </c>
+      <c r="C3803" t="n">
+        <v>66500775</v>
+      </c>
+      <c r="D3803" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/745002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3804">
+      <c r="A3804" t="inlineStr">
+        <is>
+          <t>908910</t>
+        </is>
+      </c>
+      <c r="B3804" t="inlineStr">
+        <is>
+          <t>Control alambrico YR-E17A</t>
+        </is>
+      </c>
+      <c r="C3804" t="n">
+        <v>83875.60000000001</v>
+      </c>
+      <c r="D3804" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908910</t>
+        </is>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="inlineStr">
+        <is>
+          <t>990012</t>
+        </is>
+      </c>
+      <c r="B3805" t="inlineStr">
+        <is>
+          <t>Calentador electrico 2kW</t>
+        </is>
+      </c>
+      <c r="C3805" t="n">
+        <v>44569.3</v>
+      </c>
+      <c r="D3805" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/990012</t>
+        </is>
+      </c>
+    </row>
+    <row r="3806">
+      <c r="A3806" t="inlineStr">
+        <is>
+          <t>962622</t>
+        </is>
+      </c>
+      <c r="B3806" t="inlineStr">
+        <is>
+          <t>Termom.dig.BlueStar.WT2-50+300C-14CF2WT-</t>
+        </is>
+      </c>
+      <c r="C3806" t="n">
+        <v>12963.6</v>
+      </c>
+      <c r="D3806" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/962622</t>
+        </is>
+      </c>
+    </row>
+    <row r="3807">
+      <c r="A3807" t="inlineStr">
+        <is>
+          <t>999045</t>
+        </is>
+      </c>
+      <c r="B3807" t="inlineStr">
+        <is>
+          <t>U.C.ELECTRA TTB72RA ONOFF Instalada 0041</t>
+        </is>
+      </c>
+      <c r="C3807" t="n">
+        <v>1143192.85</v>
+      </c>
+      <c r="D3807" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999045</t>
+        </is>
+      </c>
+    </row>
+    <row r="3808">
+      <c r="A3808" t="inlineStr">
+        <is>
+          <t>782116</t>
+        </is>
+      </c>
+      <c r="B3808" t="inlineStr">
+        <is>
+          <t>Rollo 100m cable taller 3x1mm-----------</t>
+        </is>
+      </c>
+      <c r="C3808" t="n">
+        <v>112837.2</v>
+      </c>
+      <c r="D3808" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782116</t>
+        </is>
+      </c>
+    </row>
+    <row r="3809">
+      <c r="A3809" t="inlineStr">
+        <is>
+          <t>906128</t>
+        </is>
+      </c>
+      <c r="B3809" t="inlineStr">
+        <is>
+          <t>Tapa vent.para bomba BlueStar-----------</t>
+        </is>
+      </c>
+      <c r="C3809" t="n">
+        <v>7700.6</v>
+      </c>
+      <c r="D3809" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906128</t>
+        </is>
+      </c>
+    </row>
+    <row r="3810">
+      <c r="A3810" t="inlineStr">
+        <is>
+          <t>911020</t>
+        </is>
+      </c>
+      <c r="B3810" t="inlineStr">
+        <is>
+          <t>Par de mensulas M520 -Epoxi ------90Kg--</t>
+        </is>
+      </c>
+      <c r="C3810" t="n">
+        <v>10941.5</v>
+      </c>
+      <c r="D3810" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911020</t>
+        </is>
+      </c>
+    </row>
+    <row r="3811">
+      <c r="A3811" t="inlineStr">
+        <is>
+          <t>937183</t>
+        </is>
+      </c>
+      <c r="B3811" t="inlineStr">
+        <is>
+          <t>PCB Assembly Filter EBR81792701</t>
+        </is>
+      </c>
+      <c r="C3811" t="n">
+        <v>142571.9</v>
+      </c>
+      <c r="D3811" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937183</t>
+        </is>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>908911</t>
+        </is>
+      </c>
+      <c r="B3812" t="inlineStr">
+        <is>
+          <t>Control alambrico color YR-E16B</t>
+        </is>
+      </c>
+      <c r="C3812" t="n">
+        <v>258814.95</v>
+      </c>
+      <c r="D3812" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908911</t>
+        </is>
+      </c>
+    </row>
+    <row r="3813">
+      <c r="A3813" t="inlineStr">
+        <is>
+          <t>942947</t>
+        </is>
+      </c>
+      <c r="B3813" t="inlineStr">
+        <is>
+          <t>Tubo Bifurc.Sal.Cond SEC008-000022(BS11-</t>
+        </is>
+      </c>
+      <c r="C3813" t="n">
+        <v>18074.25</v>
+      </c>
+      <c r="D3813" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942947</t>
+        </is>
+      </c>
+    </row>
+    <row r="3814">
+      <c r="A3814" t="inlineStr">
+        <is>
+          <t>955614</t>
+        </is>
+      </c>
+      <c r="B3814" t="inlineStr">
+        <is>
+          <t>Term.prog.ROBERTSHAW RS1100-1et.CalorSol</t>
+        </is>
+      </c>
+      <c r="C3814" t="n">
+        <v>52533.05</v>
+      </c>
+      <c r="D3814" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/955614</t>
+        </is>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="inlineStr">
+        <is>
+          <t>908006</t>
+        </is>
+      </c>
+      <c r="B3815" t="inlineStr">
+        <is>
+          <t>U.C.TADIRAN MULTI 1:3A-INV-7030w 0KM</t>
+        </is>
+      </c>
+      <c r="C3815" t="n">
+        <v>511896</v>
+      </c>
+      <c r="D3815" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908006</t>
+        </is>
+      </c>
+    </row>
+    <row r="3816">
+      <c r="A3816" t="inlineStr">
+        <is>
+          <t>942814</t>
+        </is>
+      </c>
+      <c r="B3816" t="inlineStr">
+        <is>
+          <t>Motor Cond. 40W. - Y5S613B524 (TAC12CH)</t>
+        </is>
+      </c>
+      <c r="C3816" t="n">
+        <v>72269.3</v>
+      </c>
+      <c r="D3816" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942814</t>
+        </is>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" t="inlineStr">
+        <is>
+          <t>853014</t>
+        </is>
+      </c>
+      <c r="B3817" t="inlineStr">
+        <is>
+          <t>Soporte Metal Evap. 41109-000042 TA8-32</t>
+        </is>
+      </c>
+      <c r="C3817" t="n">
+        <v>15955.2</v>
+      </c>
+      <c r="D3817" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/853014</t>
+        </is>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" t="inlineStr">
+        <is>
+          <t>979514</t>
+        </is>
+      </c>
+      <c r="B3818" t="inlineStr">
+        <is>
+          <t>U.E. Hi-wall BLUESTAR MSAFCU-18HRFN8 R32</t>
+        </is>
+      </c>
+      <c r="C3818" t="n">
+        <v>342164.25</v>
+      </c>
+      <c r="D3818" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979514</t>
+        </is>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" t="inlineStr">
+        <is>
+          <t>937176</t>
+        </is>
+      </c>
+      <c r="B3819" t="inlineStr">
+        <is>
+          <t>PCB Assembly 6871A20156J</t>
+        </is>
+      </c>
+      <c r="C3819" t="n">
+        <v>60012.05</v>
+      </c>
+      <c r="D3819" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937176</t>
+        </is>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" t="inlineStr">
+        <is>
+          <t>908912</t>
+        </is>
+      </c>
+      <c r="B3820" t="inlineStr">
+        <is>
+          <t>Ctrl central LCD 7" YCZ-A004 Max 128 IDU</t>
+        </is>
+      </c>
+      <c r="C3820" t="n">
+        <v>716986.8</v>
+      </c>
+      <c r="D3820" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/908912</t>
+        </is>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" t="inlineStr">
+        <is>
+          <t>906511</t>
+        </is>
+      </c>
+      <c r="B3821" t="inlineStr">
+        <is>
+          <t>Motoc."BlueStar"1/5 -ADW57 -R134-135W---</t>
+        </is>
+      </c>
+      <c r="C3821" t="n">
+        <v>55206.1</v>
+      </c>
+      <c r="D3821" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906511</t>
+        </is>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" t="inlineStr">
+        <is>
+          <t>906481</t>
+        </is>
+      </c>
+      <c r="B3822" t="inlineStr">
+        <is>
+          <t>Mot.Alum.BlueStar 1/4-AL-ADW66-R134-165W</t>
+        </is>
+      </c>
+      <c r="C3822" t="n">
+        <v>52851.6</v>
+      </c>
+      <c r="D3822" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906481</t>
+        </is>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" t="inlineStr">
+        <is>
+          <t>491210</t>
+        </is>
+      </c>
+      <c r="B3823" t="inlineStr">
+        <is>
+          <t>F.cobre 15g.N10-BlueStar-mol.ch.134FD15F</t>
+        </is>
+      </c>
+      <c r="C3823" t="n">
+        <v>1911.3</v>
+      </c>
+      <c r="D3823" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/491210</t>
+        </is>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" t="inlineStr">
+        <is>
+          <t>994484</t>
+        </is>
+      </c>
+      <c r="B3824" t="inlineStr">
+        <is>
+          <t>Valvula Elect.SANHUA LPF14-002----------</t>
+        </is>
+      </c>
+      <c r="C3824" t="n">
+        <v>59042.55</v>
+      </c>
+      <c r="D3824" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/994484</t>
+        </is>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" t="inlineStr">
+        <is>
+          <t>782043</t>
+        </is>
+      </c>
+      <c r="B3825" t="inlineStr">
+        <is>
+          <t>Mt.cable taller IRAM-2x1.5mm------------</t>
+        </is>
+      </c>
+      <c r="C3825" t="n">
+        <v>1294.97</v>
+      </c>
+      <c r="D3825" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/782043</t>
+        </is>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" t="inlineStr">
+        <is>
+          <t>906130</t>
+        </is>
+      </c>
+      <c r="B3826" t="inlineStr">
+        <is>
+          <t>Capacitor para bomba BlueStar-----------</t>
+        </is>
+      </c>
+      <c r="C3826" t="n">
+        <v>3033.15</v>
+      </c>
+      <c r="D3826" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906130</t>
+        </is>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" t="inlineStr">
+        <is>
+          <t>999967</t>
+        </is>
+      </c>
+      <c r="B3827" t="inlineStr">
+        <is>
+          <t>U.E.BS11INV 2300 F/C  2612 Instalada---</t>
+        </is>
+      </c>
+      <c r="C3827" t="n">
+        <v>62865.15</v>
+      </c>
+      <c r="D3827" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/999967</t>
+        </is>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" t="inlineStr">
+        <is>
+          <t>979206</t>
+        </is>
+      </c>
+      <c r="B3828" t="inlineStr">
+        <is>
+          <t>U.C. ATOM TA-V42WDHN1(AtB) 12kW---------</t>
+        </is>
+      </c>
+      <c r="C3828" t="n">
+        <v>1678883.15</v>
+      </c>
+      <c r="D3828" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979206</t>
+        </is>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" t="inlineStr">
+        <is>
+          <t>942949</t>
+        </is>
+      </c>
+      <c r="B3829" t="inlineStr">
+        <is>
+          <t>Tubo Bifurc.Ent.Cond SEC007-000027(BS11-</t>
+        </is>
+      </c>
+      <c r="C3829" t="n">
+        <v>13254.45</v>
+      </c>
+      <c r="D3829" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/942949</t>
+        </is>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" t="inlineStr">
+        <is>
+          <t>911030</t>
+        </is>
+      </c>
+      <c r="B3830" t="inlineStr">
+        <is>
+          <t>Par de mensulas M620 -Epoxi -----120Kg--</t>
+        </is>
+      </c>
+      <c r="C3830" t="n">
+        <v>17686.45</v>
+      </c>
+      <c r="D3830" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/911030</t>
+        </is>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" t="inlineStr">
+        <is>
+          <t>976902</t>
+        </is>
+      </c>
+      <c r="B3831" t="inlineStr">
+        <is>
+          <t>Tablero Elitech LS200----220--3HP WIFI--</t>
+        </is>
+      </c>
+      <c r="C3831" t="n">
+        <v>277000</v>
+      </c>
+      <c r="D3831" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/976902</t>
+        </is>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" t="inlineStr">
+        <is>
+          <t>960742</t>
+        </is>
+      </c>
+      <c r="B3832" t="inlineStr">
+        <is>
+          <t>Termost DANFOSS RT4--(-5 a30*C)-amb--vap</t>
+        </is>
+      </c>
+      <c r="C3832" t="n">
+        <v>1007559.8</v>
+      </c>
+      <c r="D3832" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/960742</t>
+        </is>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" t="inlineStr">
+        <is>
+          <t>937129</t>
+        </is>
+      </c>
+      <c r="B3833" t="inlineStr">
+        <is>
+          <t>PCB Assembly EBR75420401</t>
+        </is>
+      </c>
+      <c r="C3833" t="n">
+        <v>536355.1</v>
+      </c>
+      <c r="D3833" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937129</t>
+        </is>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" t="inlineStr">
+        <is>
+          <t>979315</t>
+        </is>
+      </c>
+      <c r="B3834" t="inlineStr">
+        <is>
+          <t>Control con cable WDC-86E/KD</t>
+        </is>
+      </c>
+      <c r="C3834" t="n">
+        <v>111312.45</v>
+      </c>
+      <c r="D3834" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/979315</t>
+        </is>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="inlineStr">
+        <is>
+          <t>937633</t>
+        </is>
+      </c>
+      <c r="B3835" t="inlineStr">
+        <is>
+          <t>Evap. Assembly 5421A20218B - AMNH07GD4L0</t>
+        </is>
+      </c>
+      <c r="C3835" t="n">
+        <v>43835.25</v>
+      </c>
+      <c r="D3835" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/937633</t>
+        </is>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="inlineStr">
+        <is>
+          <t>913709</t>
+        </is>
+      </c>
+      <c r="B3836" t="inlineStr">
+        <is>
+          <t>Sella Fuga A/A ECTREME 30ml--TR1062C01S2</t>
+        </is>
+      </c>
+      <c r="C3836" t="n">
+        <v>20234.85</v>
+      </c>
+      <c r="D3836" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/913709</t>
+        </is>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" t="inlineStr">
+        <is>
+          <t>488102</t>
+        </is>
+      </c>
+      <c r="B3837" t="inlineStr">
+        <is>
+          <t>Bolsa 100 Prec.PTFL4-200-200mmx4.6mm-BLA</t>
+        </is>
+      </c>
+      <c r="C3837" t="n">
+        <v>4293.5</v>
+      </c>
+      <c r="D3837" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/488102</t>
+        </is>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" t="inlineStr">
+        <is>
+          <t>971048</t>
+        </is>
+      </c>
+      <c r="B3838" t="inlineStr">
+        <is>
+          <t>Manom.BlueStar-1527H-alta-R410-------d80</t>
+        </is>
+      </c>
+      <c r="C3838" t="n">
+        <v>5553.85</v>
+      </c>
+      <c r="D3838" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/971048</t>
+        </is>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" t="inlineStr">
+        <is>
+          <t>940613</t>
+        </is>
+      </c>
+      <c r="B3839" t="inlineStr">
+        <is>
+          <t>Balanza Dig.Bluetooth VALUE VRS50i01-50K</t>
+        </is>
+      </c>
+      <c r="C3839" t="n">
+        <v>218345.25</v>
+      </c>
+      <c r="D3839" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/940613</t>
+        </is>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" t="inlineStr">
+        <is>
+          <t>906522</t>
+        </is>
+      </c>
+      <c r="B3840" t="inlineStr">
+        <is>
+          <t>Motoc.BlueStar 1/4 MLGQR55K-B404--------</t>
+        </is>
+      </c>
+      <c r="C3840" t="n">
+        <v>97600.95</v>
+      </c>
+      <c r="D3840" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/906522</t>
+        </is>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" t="inlineStr">
+        <is>
+          <t>174486</t>
+        </is>
+      </c>
+      <c r="B3841" t="inlineStr">
+        <is>
+          <t>Balde 10lts -LDV NEW-Desodorante p/cond-</t>
+        </is>
+      </c>
+      <c r="C3841" t="n">
+        <v>35524.23</v>
+      </c>
+      <c r="D3841" t="inlineStr">
+        <is>
+          <t>https://www.ansal.com.ar/producto/174486</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
